--- a/bts-gpme/tp-1083/ressources/R08_Fournisseurs_qualite_et_projet.xlsx
+++ b/bts-gpme/tp-1083/ressources/R08_Fournisseurs_qualite_et_projet.xlsx
@@ -2,10 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Retours_clients" sheetId="1" r:id="R9c9b5bf9f5684bbf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fournisseurs_criticite" sheetId="2" r:id="R898a40c47561437c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Projet_actions" sheetId="3" r:id="R97d86b3e8d9947e1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lire_ce_classeur" sheetId="4" r:id="Rdca9fcb4939a48b4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Retours_clients" sheetId="1" r:id="Rb90d34adae304c7f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fournisseurs_criticite" sheetId="2" r:id="Ra4bdea27900f4d25"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Projet_actions" sheetId="3" r:id="Rf21416d2f14341d3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lire_ce_classeur" sheetId="4" r:id="R120e73db2c7e4a1c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Analyse_dependances" sheetId="5" r:id="Re3eac6009dae48b1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Veille_S5" sheetId="6" r:id="R2629d323550d4d8f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Projet_initial" sheetId="7" r:id="R6e71ce5b437144de"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Volumes_exposition" sheetId="8" r:id="R2f4306e9c8f94615"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Diagnostic_complementaire" sheetId="9" r:id="Rdfd25310ec6f43f3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Suivi_pilote" sheetId="10" r:id="Rfa20d5a7f4a547e7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Capitalisation_REX" sheetId="11" r:id="Rc7a48a00a8a04893"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -16,12 +23,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="3">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="dd/mm/yyyy"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00 &quot;€&quot;"/>
     <x:numFmt numFmtId="202" formatCode="0%"/>
+    <x:numFmt numFmtId="203" formatCode="0.00%"/>
   </x:numFmts>
-  <x:fonts count="5">
+  <x:fonts count="7">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -50,8 +58,18 @@
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF6A4A00"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF244E2E"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="6">
+  <x:fills count="19">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -78,6 +96,71 @@
         <x:fgColor rgb="FF3C7465"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF3CD"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9EAF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE8F3E8"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEAF2F8"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEAF2F8"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9EAF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF3CD"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE8F3E8"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEAF2F8"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="2">
     <x:border/>
@@ -86,7 +169,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="123">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -154,6 +237,196 @@
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="201" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="201" fontId="2" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="2" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="2" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="201" fontId="2" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="201" fontId="2" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="2" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="2" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="201" fontId="0" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="201" fontId="2" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="2" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="2" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -5047,8 +5320,537 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R79d42d93a81e4a6c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9052a213292d492c"/>
   </x:tableParts>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="16" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="16" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="16" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="22" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="19" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="22" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="22" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="44" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="46" customHeight="1">
+      <x:c r="A1" s="95" t="str">
+        <x:v>SITUATION 6 — SUIVI DU PILOTE SUR QUATRE SEMAINES. Données fictives de suivi.</x:v>
+      </x:c>
+      <x:c r="B1" s="95"/>
+      <x:c r="C1" s="95"/>
+      <x:c r="D1" s="95"/>
+      <x:c r="E1" s="95"/>
+      <x:c r="F1" s="95"/>
+      <x:c r="G1" s="95"/>
+      <x:c r="H1" s="95"/>
+      <x:c r="I1" s="95"/>
+      <x:c r="J1" s="95"/>
+    </x:row>
+    <x:row r="2" ht="46" customHeight="1">
+      <x:c r="A2" s="98" t="str">
+        <x:v>Le suivi concerne la couture de la référence J-101 sur le périmètre ciblé après ajustement du contrôle. Calculez les taux et construisez vous-même la synthèse des quatre semaines. Les retours clients peuvent être décalés dans le temps : une amélioration observée sur quatre semaines doit encore être confirmée.</x:v>
+      </x:c>
+      <x:c r="B2" s="98" t="str">
+        <x:v>Le suivi concerne la couture de la référence J-101 sur le périmètre ciblé après ajustement du contrôle. Calculez les taux et construisez vous-même la synthèse des quatre semaines. Les retours clients peuvent être décalés dans le temps : une amélioration observée sur quatre semaines doit encore être confirmée.</x:v>
+      </x:c>
+      <x:c r="C2" s="98" t="str">
+        <x:v>Le suivi concerne la couture de la référence J-101 sur le périmètre ciblé après ajustement du contrôle. Calculez les taux et construisez vous-même la synthèse des quatre semaines. Les retours clients peuvent être décalés dans le temps : une amélioration observée sur quatre semaines doit encore être confirmée.</x:v>
+      </x:c>
+      <x:c r="D2" s="98" t="str">
+        <x:v>Le suivi concerne la couture de la référence J-101 sur le périmètre ciblé après ajustement du contrôle. Calculez les taux et construisez vous-même la synthèse des quatre semaines. Les retours clients peuvent être décalés dans le temps : une amélioration observée sur quatre semaines doit encore être confirmée.</x:v>
+      </x:c>
+      <x:c r="E2" s="98" t="str">
+        <x:v>Le suivi concerne la couture de la référence J-101 sur le périmètre ciblé après ajustement du contrôle. Calculez les taux et construisez vous-même la synthèse des quatre semaines. Les retours clients peuvent être décalés dans le temps : une amélioration observée sur quatre semaines doit encore être confirmée.</x:v>
+      </x:c>
+      <x:c r="F2" s="98" t="str">
+        <x:v>Le suivi concerne la couture de la référence J-101 sur le périmètre ciblé après ajustement du contrôle. Calculez les taux et construisez vous-même la synthèse des quatre semaines. Les retours clients peuvent être décalés dans le temps : une amélioration observée sur quatre semaines doit encore être confirmée.</x:v>
+      </x:c>
+      <x:c r="G2" s="98" t="str">
+        <x:v>Le suivi concerne la couture de la référence J-101 sur le périmètre ciblé après ajustement du contrôle. Calculez les taux et construisez vous-même la synthèse des quatre semaines. Les retours clients peuvent être décalés dans le temps : une amélioration observée sur quatre semaines doit encore être confirmée.</x:v>
+      </x:c>
+      <x:c r="H2" s="98" t="str">
+        <x:v>Le suivi concerne la couture de la référence J-101 sur le périmètre ciblé après ajustement du contrôle. Calculez les taux et construisez vous-même la synthèse des quatre semaines. Les retours clients peuvent être décalés dans le temps : une amélioration observée sur quatre semaines doit encore être confirmée.</x:v>
+      </x:c>
+      <x:c r="I2" s="98" t="str">
+        <x:v>Le suivi concerne la couture de la référence J-101 sur le périmètre ciblé après ajustement du contrôle. Calculez les taux et construisez vous-même la synthèse des quatre semaines. Les retours clients peuvent être décalés dans le temps : une amélioration observée sur quatre semaines doit encore être confirmée.</x:v>
+      </x:c>
+      <x:c r="J2" s="98" t="str">
+        <x:v>Le suivi concerne la couture de la référence J-101 sur le périmètre ciblé après ajustement du contrôle. Calculez les taux et construisez vous-même la synthèse des quatre semaines. Les retours clients peuvent être décalés dans le temps : une amélioration observée sur quatre semaines doit encore être confirmée.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="50" customHeight="1">
+      <x:c r="A4" s="92" t="str">
+        <x:v>Période</x:v>
+      </x:c>
+      <x:c r="B4" s="92" t="str">
+        <x:v>Unités exposées</x:v>
+      </x:c>
+      <x:c r="C4" s="92" t="str">
+        <x:v>Retours couture</x:v>
+      </x:c>
+      <x:c r="D4" s="92" t="str">
+        <x:v>Taux de retours</x:v>
+      </x:c>
+      <x:c r="E4" s="92" t="str">
+        <x:v>Pièces contrôlées en fin de ligne</x:v>
+      </x:c>
+      <x:c r="F4" s="92" t="str">
+        <x:v>NC couture détectées</x:v>
+      </x:c>
+      <x:c r="G4" s="92" t="str">
+        <x:v>Taux NC au contrôle</x:v>
+      </x:c>
+      <x:c r="H4" s="92" t="str">
+        <x:v>Contrôles de démarrage tracés</x:v>
+      </x:c>
+      <x:c r="I4" s="92" t="str">
+        <x:v>Temps additionnel moyen / lot</x:v>
+      </x:c>
+      <x:c r="J4" s="92" t="str">
+        <x:v>Observation</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="60" customHeight="1">
+      <x:c r="A5" s="50" t="str">
+        <x:v>Référence avant pilote</x:v>
+      </x:c>
+      <x:c r="B5" s="50" t="n">
+        <x:v>520</x:v>
+      </x:c>
+      <x:c r="C5" s="50" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="D5" s="105"/>
+      <x:c r="E5" s="50" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="F5" s="50" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G5" s="105"/>
+      <x:c r="H5" s="50" t="str">
+        <x:v>NE</x:v>
+      </x:c>
+      <x:c r="I5" s="50" t="str">
+        <x:v>NE</x:v>
+      </x:c>
+      <x:c r="J5" s="50" t="str">
+        <x:v>Périmètre J-101 · L26-08 · Atelier C ; base de comparaison.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="60" customHeight="1">
+      <x:c r="A6" s="50" t="str">
+        <x:v>Semaine 1</x:v>
+      </x:c>
+      <x:c r="B6" s="50" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="C6" s="50" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D6" s="105"/>
+      <x:c r="E6" s="50" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="F6" s="50" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G6" s="105"/>
+      <x:c r="H6" s="107" t="n">
+        <x:v>0.8</x:v>
+      </x:c>
+      <x:c r="I6" s="50" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="J6" s="50" t="str">
+        <x:v>5 contrôles de démarrage prévus ; 4 tracés.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="60" customHeight="1">
+      <x:c r="A7" s="50" t="str">
+        <x:v>Semaine 2</x:v>
+      </x:c>
+      <x:c r="B7" s="50" t="n">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="C7" s="50" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D7" s="105"/>
+      <x:c r="E7" s="50" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="F7" s="50" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G7" s="105"/>
+      <x:c r="H7" s="107" t="n">
+        <x:v>0.95</x:v>
+      </x:c>
+      <x:c r="I7" s="50" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="J7" s="50" t="str">
+        <x:v>20 contrôles de démarrage prévus ; 19 tracés.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="60" customHeight="1">
+      <x:c r="A8" s="50" t="str">
+        <x:v>Semaine 3</x:v>
+      </x:c>
+      <x:c r="B8" s="50" t="n">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="C8" s="50" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D8" s="105"/>
+      <x:c r="E8" s="50" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="F8" s="50" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G8" s="105"/>
+      <x:c r="H8" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I8" s="50" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="J8" s="50" t="str">
+        <x:v>20 contrôles de démarrage prévus ; 20 tracés.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="60" customHeight="1">
+      <x:c r="A9" s="50" t="str">
+        <x:v>Semaine 4</x:v>
+      </x:c>
+      <x:c r="B9" s="50" t="n">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="C9" s="50" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D9" s="105"/>
+      <x:c r="E9" s="50" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="F9" s="50" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G9" s="105"/>
+      <x:c r="H9" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I9" s="50" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J9" s="50" t="str">
+        <x:v>20 contrôles de démarrage prévus ; 20 tracés.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="50"/>
+      <x:c r="B10" s="50"/>
+      <x:c r="C10" s="50"/>
+      <x:c r="D10" s="105"/>
+      <x:c r="E10" s="50"/>
+      <x:c r="F10" s="50"/>
+      <x:c r="G10" s="105"/>
+      <x:c r="H10" s="50"/>
+      <x:c r="I10" s="50"/>
+      <x:c r="J10" s="50"/>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="104" t="str">
+        <x:v>Total / synthèse pilote (S1 à S4)</x:v>
+      </x:c>
+      <x:c r="B11" s="104"/>
+      <x:c r="C11" s="104"/>
+      <x:c r="D11" s="106"/>
+      <x:c r="E11" s="104"/>
+      <x:c r="F11" s="104"/>
+      <x:c r="G11" s="106"/>
+      <x:c r="H11" s="104"/>
+      <x:c r="I11" s="104"/>
+      <x:c r="J11" s="104"/>
+    </x:row>
+    <x:row r="13" ht="48" customHeight="1">
+      <x:c r="A13" s="98" t="str">
+        <x:v>À interpréter : comparez la situation de référence et le pilote, mais tenez compte du décalage possible des retours clients, de la durée limitée et de la taille des échantillons.</x:v>
+      </x:c>
+      <x:c r="B13" s="98"/>
+      <x:c r="C13" s="98"/>
+      <x:c r="D13" s="98"/>
+      <x:c r="E13" s="98"/>
+      <x:c r="F13" s="98"/>
+      <x:c r="G13" s="98"/>
+      <x:c r="H13" s="98"/>
+      <x:c r="I13" s="98"/>
+      <x:c r="J13" s="98"/>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:J1"/>
+    <x:mergeCell ref="A2:J2"/>
+    <x:mergeCell ref="A13:J13"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="22" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="22" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="22" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="46" customHeight="1">
+      <x:c r="A1" s="95" t="str">
+        <x:v>SITUATION 6 — FICHE DE RETOUR D’EXPÉRIENCE / CAPITALISATION</x:v>
+      </x:c>
+      <x:c r="B1" s="95"/>
+      <x:c r="C1" s="95"/>
+      <x:c r="D1" s="95"/>
+      <x:c r="E1" s="95"/>
+      <x:c r="F1" s="95"/>
+    </x:row>
+    <x:row r="2" ht="46" customHeight="1">
+      <x:c r="A2" s="98" t="str">
+        <x:v>Ne renseignez comme « cause validée » ou « efficacité démontrée » que ce que les preuves permettent réellement d’affirmer. Si le recul est insuffisant, indiquez « à confirmer » et programmez une nouvelle vérification.</x:v>
+      </x:c>
+      <x:c r="B2" s="98"/>
+      <x:c r="C2" s="98"/>
+      <x:c r="D2" s="98"/>
+      <x:c r="E2" s="98"/>
+      <x:c r="F2" s="98"/>
+    </x:row>
+    <x:row r="4" ht="42" customHeight="1">
+      <x:c r="A4" s="117" t="str">
+        <x:v>Identifiant / date du REX</x:v>
+      </x:c>
+      <x:c r="B4" s="117"/>
+      <x:c r="C4" s="50"/>
+      <x:c r="D4" s="50"/>
+      <x:c r="E4" s="50"/>
+      <x:c r="F4" s="50"/>
+    </x:row>
+    <x:row r="5" ht="42" customHeight="1">
+      <x:c r="A5" s="117" t="str">
+        <x:v>Objet et périmètre</x:v>
+      </x:c>
+      <x:c r="B5" s="117"/>
+      <x:c r="C5" s="50"/>
+      <x:c r="D5" s="50"/>
+      <x:c r="E5" s="50"/>
+      <x:c r="F5" s="50"/>
+    </x:row>
+    <x:row r="6" ht="42" customHeight="1">
+      <x:c r="A6" s="117" t="str">
+        <x:v>Faits établis et sources</x:v>
+      </x:c>
+      <x:c r="B6" s="117"/>
+      <x:c r="C6" s="50"/>
+      <x:c r="D6" s="50"/>
+      <x:c r="E6" s="50"/>
+      <x:c r="F6" s="50"/>
+    </x:row>
+    <x:row r="7" ht="42" customHeight="1">
+      <x:c r="A7" s="117" t="str">
+        <x:v>Impacts mesurés</x:v>
+      </x:c>
+      <x:c r="B7" s="117"/>
+      <x:c r="C7" s="50"/>
+      <x:c r="D7" s="50"/>
+      <x:c r="E7" s="50"/>
+      <x:c r="F7" s="50"/>
+    </x:row>
+    <x:row r="8" ht="42" customHeight="1">
+      <x:c r="A8" s="117" t="str">
+        <x:v>Hypothèses examinées</x:v>
+      </x:c>
+      <x:c r="B8" s="117"/>
+      <x:c r="C8" s="50"/>
+      <x:c r="D8" s="50"/>
+      <x:c r="E8" s="50"/>
+      <x:c r="F8" s="50"/>
+    </x:row>
+    <x:row r="9" ht="42" customHeight="1">
+      <x:c r="A9" s="117" t="str">
+        <x:v>Cause(s) retenue(s) et niveau de confiance</x:v>
+      </x:c>
+      <x:c r="B9" s="117"/>
+      <x:c r="C9" s="50"/>
+      <x:c r="D9" s="50"/>
+      <x:c r="E9" s="50"/>
+      <x:c r="F9" s="50"/>
+    </x:row>
+    <x:row r="10" ht="42" customHeight="1">
+      <x:c r="A10" s="117" t="str">
+        <x:v>Action(s) testée(s)</x:v>
+      </x:c>
+      <x:c r="B10" s="117"/>
+      <x:c r="C10" s="50"/>
+      <x:c r="D10" s="50"/>
+      <x:c r="E10" s="50"/>
+      <x:c r="F10" s="50"/>
+    </x:row>
+    <x:row r="11" ht="42" customHeight="1">
+      <x:c r="A11" s="117" t="str">
+        <x:v>Indicateur de référence (avant)</x:v>
+      </x:c>
+      <x:c r="B11" s="117"/>
+      <x:c r="C11" s="50"/>
+      <x:c r="D11" s="50"/>
+      <x:c r="E11" s="50"/>
+      <x:c r="F11" s="50"/>
+    </x:row>
+    <x:row r="12" ht="42" customHeight="1">
+      <x:c r="A12" s="117" t="str">
+        <x:v>Cible / critère de réussite</x:v>
+      </x:c>
+      <x:c r="B12" s="117"/>
+      <x:c r="C12" s="50"/>
+      <x:c r="D12" s="50"/>
+      <x:c r="E12" s="50"/>
+      <x:c r="F12" s="50"/>
+    </x:row>
+    <x:row r="13" ht="42" customHeight="1">
+      <x:c r="A13" s="117" t="str">
+        <x:v>Résultat observé</x:v>
+      </x:c>
+      <x:c r="B13" s="117"/>
+      <x:c r="C13" s="50"/>
+      <x:c r="D13" s="50"/>
+      <x:c r="E13" s="50"/>
+      <x:c r="F13" s="50"/>
+    </x:row>
+    <x:row r="14" ht="42" customHeight="1">
+      <x:c r="A14" s="117" t="str">
+        <x:v>Conclusion sur l’efficacité</x:v>
+      </x:c>
+      <x:c r="B14" s="117"/>
+      <x:c r="C14" s="50"/>
+      <x:c r="D14" s="50"/>
+      <x:c r="E14" s="50"/>
+      <x:c r="F14" s="50"/>
+    </x:row>
+    <x:row r="15" ht="42" customHeight="1">
+      <x:c r="A15" s="117" t="str">
+        <x:v>Limites / informations encore manquantes</x:v>
+      </x:c>
+      <x:c r="B15" s="117"/>
+      <x:c r="C15" s="50"/>
+      <x:c r="D15" s="50"/>
+      <x:c r="E15" s="50"/>
+      <x:c r="F15" s="50"/>
+    </x:row>
+    <x:row r="16" ht="42" customHeight="1">
+      <x:c r="A16" s="117" t="str">
+        <x:v>Décision : généraliser / ajuster / arrêter / poursuivre le test</x:v>
+      </x:c>
+      <x:c r="B16" s="117"/>
+      <x:c r="C16" s="50"/>
+      <x:c r="D16" s="50"/>
+      <x:c r="E16" s="50"/>
+      <x:c r="F16" s="50"/>
+    </x:row>
+    <x:row r="17" ht="42" customHeight="1">
+      <x:c r="A17" s="117" t="str">
+        <x:v>Documents et preuves liés / emplacement</x:v>
+      </x:c>
+      <x:c r="B17" s="117"/>
+      <x:c r="C17" s="50"/>
+      <x:c r="D17" s="50"/>
+      <x:c r="E17" s="50"/>
+      <x:c r="F17" s="50"/>
+    </x:row>
+    <x:row r="18" ht="42" customHeight="1">
+      <x:c r="A18" s="117" t="str">
+        <x:v>Personne référente</x:v>
+      </x:c>
+      <x:c r="B18" s="117"/>
+      <x:c r="C18" s="50"/>
+      <x:c r="D18" s="50"/>
+      <x:c r="E18" s="50"/>
+      <x:c r="F18" s="50"/>
+    </x:row>
+    <x:row r="19" ht="42" customHeight="1">
+      <x:c r="A19" s="117" t="str">
+        <x:v>Date de réexamen</x:v>
+      </x:c>
+      <x:c r="B19" s="117"/>
+      <x:c r="C19" s="50"/>
+      <x:c r="D19" s="50"/>
+      <x:c r="E19" s="50"/>
+      <x:c r="F19" s="50"/>
+    </x:row>
+    <x:row r="20" ht="42" customHeight="1">
+      <x:c r="A20" s="117" t="str">
+        <x:v>Enseignement réutilisable pour un cas futur</x:v>
+      </x:c>
+      <x:c r="B20" s="117"/>
+      <x:c r="C20" s="50"/>
+      <x:c r="D20" s="50"/>
+      <x:c r="E20" s="50"/>
+      <x:c r="F20" s="50"/>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:F1"/>
+    <x:mergeCell ref="A2:F2"/>
+    <x:mergeCell ref="A4:B4"/>
+    <x:mergeCell ref="C4:F4"/>
+    <x:mergeCell ref="A5:B5"/>
+    <x:mergeCell ref="C5:F5"/>
+    <x:mergeCell ref="A6:B6"/>
+    <x:mergeCell ref="C6:F6"/>
+    <x:mergeCell ref="A7:B7"/>
+    <x:mergeCell ref="C7:F7"/>
+    <x:mergeCell ref="A8:B8"/>
+    <x:mergeCell ref="C8:F8"/>
+    <x:mergeCell ref="A9:B9"/>
+    <x:mergeCell ref="C9:F9"/>
+    <x:mergeCell ref="A10:B10"/>
+    <x:mergeCell ref="C10:F10"/>
+    <x:mergeCell ref="A11:B11"/>
+    <x:mergeCell ref="C11:F11"/>
+    <x:mergeCell ref="A12:B12"/>
+    <x:mergeCell ref="C12:F12"/>
+    <x:mergeCell ref="A13:B13"/>
+    <x:mergeCell ref="C13:F13"/>
+    <x:mergeCell ref="A14:B14"/>
+    <x:mergeCell ref="C14:F14"/>
+    <x:mergeCell ref="A15:B15"/>
+    <x:mergeCell ref="C15:F15"/>
+    <x:mergeCell ref="A16:B16"/>
+    <x:mergeCell ref="C16:F16"/>
+    <x:mergeCell ref="A17:B17"/>
+    <x:mergeCell ref="C17:F17"/>
+    <x:mergeCell ref="A18:B18"/>
+    <x:mergeCell ref="C18:F18"/>
+    <x:mergeCell ref="A19:B19"/>
+    <x:mergeCell ref="C19:F19"/>
+    <x:mergeCell ref="A20:B20"/>
+    <x:mergeCell ref="C20:F20"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
 
@@ -5084,6 +5886,21 @@
       <x:c r="J1"/>
       <x:c r="K1"/>
     </x:row>
+    <x:row r="2" ht="50" customHeight="1">
+      <x:c r="A2" s="40" t="str">
+        <x:v>À interpréter avec prudence : un incident récent n’est pas synonyme de dépendance critique, et l’absence d’incident ne prouve pas une faible dépendance. Les colonnes « Certification / preuve » et « Impact environnemental à surveiller » alimentent la veille ; elles ne doivent pas être ajoutées mécaniquement à un score de dépendance.</x:v>
+      </x:c>
+      <x:c r="B2" s="40"/>
+      <x:c r="C2" s="40"/>
+      <x:c r="D2" s="40"/>
+      <x:c r="E2" s="40"/>
+      <x:c r="F2" s="40"/>
+      <x:c r="G2" s="40"/>
+      <x:c r="H2" s="40"/>
+      <x:c r="I2" s="40"/>
+      <x:c r="J2" s="40"/>
+      <x:c r="K2" s="40"/>
+    </x:row>
     <x:row r="3">
       <x:c r="A3" s="14" t="str">
         <x:v>Partenaire pédagogique</x:v>
@@ -5472,10 +6289,11 @@
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:H1"/>
+    <x:mergeCell ref="A2:K2"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4410149daed0416e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re9a10285b2b04d5c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5484,242 +6302,298 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="42" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="28" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="20" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="28" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="16" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="16" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="16" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="16" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="24" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="24" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="16" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="28" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="32" customHeight="1">
-      <x:c r="A1" s="6" t="str">
-        <x:v>TRAME DU PROJET DU SCÉNARIO — à ne pas confondre avec le Kanban utilisé par votre groupe pour organiser son propre travail.</x:v>
-      </x:c>
-      <x:c r="B1"/>
-      <x:c r="C1"/>
-      <x:c r="D1"/>
-      <x:c r="E1"/>
-      <x:c r="F1"/>
-      <x:c r="G1"/>
-      <x:c r="H1"/>
+    <x:row r="1" ht="46" customHeight="1">
+      <x:c r="A1" s="109" t="str">
+        <x:v>SITUATION 6 — PLAN D’ACTIONS QUALITÉ APRÈS DIAGNOSTIC. Ne renseignez les actions détaillées qu’après avoir exploité les preuves disponibles.</x:v>
+      </x:c>
+      <x:c r="B1" s="109"/>
+      <x:c r="C1" s="109"/>
+      <x:c r="D1" s="109"/>
+      <x:c r="E1" s="109"/>
+      <x:c r="F1" s="109"/>
+      <x:c r="G1" s="109"/>
+      <x:c r="H1" s="109"/>
+      <x:c r="I1" s="95"/>
+      <x:c r="J1" s="95"/>
+      <x:c r="K1" s="95"/>
+      <x:c r="L1" s="95"/>
+    </x:row>
+    <x:row r="2" ht="46" customHeight="1">
+      <x:c r="A2" s="98" t="str">
+        <x:v>Le planning initial de la situation 5 reste dans « Projet_initial ». Ici, vous transformez le diagnostic en actions testables, puis vous suivez coûts, résultats et décisions.</x:v>
+      </x:c>
+      <x:c r="B2" s="98"/>
+      <x:c r="C2" s="98"/>
+      <x:c r="D2" s="98"/>
+      <x:c r="E2" s="98"/>
+      <x:c r="F2" s="98"/>
+      <x:c r="G2" s="98"/>
+      <x:c r="H2" s="98"/>
+      <x:c r="I2" s="98"/>
+      <x:c r="J2" s="98"/>
+      <x:c r="K2" s="98"/>
+      <x:c r="L2" s="98"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="14" t="str">
+      <x:c r="A3" s="14"/>
+      <x:c r="B3" s="14"/>
+      <x:c r="C3" s="14"/>
+      <x:c r="D3" s="14"/>
+      <x:c r="E3" s="14"/>
+      <x:c r="F3" s="14"/>
+      <x:c r="G3" s="14"/>
+      <x:c r="H3" s="14"/>
+    </x:row>
+    <x:row r="4" ht="44" customHeight="1">
+      <x:c r="A4" s="92" t="str">
         <x:v>Action / tâche</x:v>
       </x:c>
-      <x:c r="B3" s="14" t="str">
+      <x:c r="B4" s="92" t="str">
         <x:v>Responsable</x:v>
       </x:c>
-      <x:c r="C3" s="14" t="str">
-        <x:v>Durée estimée (jours)</x:v>
-      </x:c>
-      <x:c r="D3" s="14" t="str">
+      <x:c r="C4" s="92" t="str">
         <x:v>Prédécesseur</x:v>
       </x:c>
-      <x:c r="E3" s="14" t="str">
-        <x:v>Date début prévue</x:v>
-      </x:c>
-      <x:c r="F3" s="14" t="str">
-        <x:v>Date fin prévue</x:v>
-      </x:c>
-      <x:c r="G3" s="14" t="str">
-        <x:v>Indicateur de réussite</x:v>
-      </x:c>
-      <x:c r="H3" s="14" t="str">
+      <x:c r="D4" s="92" t="str">
+        <x:v>Début prévu</x:v>
+      </x:c>
+      <x:c r="E4" s="92" t="str">
+        <x:v>Fin prévue</x:v>
+      </x:c>
+      <x:c r="F4" s="92" t="str">
+        <x:v>Coût prévu (€)</x:v>
+      </x:c>
+      <x:c r="G4" s="92" t="str">
+        <x:v>Coût réel (€)</x:v>
+      </x:c>
+      <x:c r="H4" s="92" t="str">
+        <x:v>Indicateur</x:v>
+      </x:c>
+      <x:c r="I4" s="92" t="str">
+        <x:v>Cible</x:v>
+      </x:c>
+      <x:c r="J4" s="92" t="str">
+        <x:v>Résultat observé</x:v>
+      </x:c>
+      <x:c r="K4" s="92" t="str">
         <x:v>Statut</x:v>
       </x:c>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="20" t="str">
-        <x:v>Valider le diagnostic à partir des retours</x:v>
-      </x:c>
-      <x:c r="B4" s="20" t="str">
-        <x:v>À attribuer</x:v>
-      </x:c>
-      <x:c r="C4" s="20" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D4" s="20" t="str">
-        <x:v>-</x:v>
-      </x:c>
-      <x:c r="E4" s="20"/>
-      <x:c r="F4" s="20"/>
-      <x:c r="G4" s="20" t="str">
-        <x:v>Causes prioritaires validées</x:v>
-      </x:c>
-      <x:c r="H4" s="20" t="str">
-        <x:v>À faire</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5">
-      <x:c r="A5" s="20" t="str">
-        <x:v>Contrôler le lot et les stocks concernés</x:v>
-      </x:c>
-      <x:c r="B5" s="20" t="str">
-        <x:v>À attribuer</x:v>
-      </x:c>
-      <x:c r="C5" s="20" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D5" s="20" t="str">
-        <x:v>Diagnostic</x:v>
-      </x:c>
-      <x:c r="E5" s="20"/>
-      <x:c r="F5" s="20"/>
-      <x:c r="G5" s="20" t="str">
-        <x:v>% stock contrôlé</x:v>
-      </x:c>
-      <x:c r="H5" s="20" t="str">
-        <x:v>À faire</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6">
-      <x:c r="A6" s="20" t="str">
-        <x:v>Réunir atelier + qualité + SAV</x:v>
-      </x:c>
-      <x:c r="B6" s="20" t="str">
-        <x:v>À attribuer</x:v>
-      </x:c>
-      <x:c r="C6" s="20" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D6" s="20" t="str">
-        <x:v>Diagnostic</x:v>
-      </x:c>
-      <x:c r="E6" s="20"/>
-      <x:c r="F6" s="20"/>
-      <x:c r="G6" s="20" t="str">
-        <x:v>Décision tracée</x:v>
-      </x:c>
-      <x:c r="H6" s="20" t="str">
-        <x:v>À faire</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7">
-      <x:c r="A7" s="20" t="str">
-        <x:v>Tester une modification de contrôle en fin de ligne</x:v>
-      </x:c>
-      <x:c r="B7" s="20" t="str">
-        <x:v>À attribuer</x:v>
-      </x:c>
-      <x:c r="C7" s="20" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D7" s="20" t="str">
-        <x:v>Réunion</x:v>
-      </x:c>
-      <x:c r="E7" s="20"/>
-      <x:c r="F7" s="20"/>
-      <x:c r="G7" s="20" t="str">
-        <x:v>Taux défaut test</x:v>
-      </x:c>
-      <x:c r="H7" s="20" t="str">
-        <x:v>À faire</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8">
-      <x:c r="A8" s="20" t="str">
-        <x:v>Mettre à jour la procédure de contrôle</x:v>
-      </x:c>
-      <x:c r="B8" s="20" t="str">
-        <x:v>À attribuer</x:v>
-      </x:c>
-      <x:c r="C8" s="20" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D8" s="20" t="str">
-        <x:v>Test</x:v>
-      </x:c>
-      <x:c r="E8" s="20"/>
-      <x:c r="F8" s="20"/>
-      <x:c r="G8" s="20" t="str">
-        <x:v>Procédure validée</x:v>
-      </x:c>
-      <x:c r="H8" s="20" t="str">
-        <x:v>À faire</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" s="20" t="str">
-        <x:v>Former les opérateurs concernés</x:v>
-      </x:c>
-      <x:c r="B9" s="20" t="str">
-        <x:v>À attribuer</x:v>
-      </x:c>
-      <x:c r="C9" s="20" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D9" s="20" t="str">
-        <x:v>Procédure</x:v>
-      </x:c>
-      <x:c r="E9" s="20"/>
-      <x:c r="F9" s="20"/>
-      <x:c r="G9" s="20" t="str">
-        <x:v>% personnes formées</x:v>
-      </x:c>
-      <x:c r="H9" s="20" t="str">
-        <x:v>À faire</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10">
-      <x:c r="A10" s="20" t="str">
-        <x:v>Suivre 4 semaines d'indicateurs</x:v>
-      </x:c>
-      <x:c r="B10" s="20" t="str">
-        <x:v>À attribuer</x:v>
-      </x:c>
-      <x:c r="C10" s="20" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D10" s="20" t="str">
-        <x:v>Formation</x:v>
-      </x:c>
-      <x:c r="E10" s="20"/>
-      <x:c r="F10" s="20"/>
-      <x:c r="G10" s="20" t="str">
-        <x:v>Taux de retour / 100 ventes</x:v>
-      </x:c>
-      <x:c r="H10" s="20" t="str">
-        <x:v>À faire</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11">
-      <x:c r="A11" s="20" t="str">
-        <x:v>Faire le bilan et capitaliser</x:v>
-      </x:c>
-      <x:c r="B11" s="20" t="str">
-        <x:v>À attribuer</x:v>
-      </x:c>
-      <x:c r="C11" s="20" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D11" s="20" t="str">
-        <x:v>Suivi</x:v>
-      </x:c>
-      <x:c r="E11" s="20"/>
-      <x:c r="F11" s="20"/>
-      <x:c r="G11" s="20" t="str">
-        <x:v>Retour d'expérience rédigé</x:v>
-      </x:c>
-      <x:c r="H11" s="20" t="str">
-        <x:v>À faire</x:v>
+      <x:c r="L4" s="92" t="str">
+        <x:v>Décision / arbitrage</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="42" customHeight="1">
+      <x:c r="A5" s="50"/>
+      <x:c r="B5" s="50"/>
+      <x:c r="C5" s="50"/>
+      <x:c r="D5" s="62"/>
+      <x:c r="E5" s="62"/>
+      <x:c r="F5" s="70"/>
+      <x:c r="G5" s="70"/>
+      <x:c r="H5" s="50"/>
+      <x:c r="I5" s="50"/>
+      <x:c r="J5" s="50"/>
+      <x:c r="K5" s="50"/>
+      <x:c r="L5" s="50"/>
+    </x:row>
+    <x:row r="6" ht="42" customHeight="1">
+      <x:c r="A6" s="50"/>
+      <x:c r="B6" s="50"/>
+      <x:c r="C6" s="50"/>
+      <x:c r="D6" s="62"/>
+      <x:c r="E6" s="62"/>
+      <x:c r="F6" s="70"/>
+      <x:c r="G6" s="70"/>
+      <x:c r="H6" s="50"/>
+      <x:c r="I6" s="50"/>
+      <x:c r="J6" s="50"/>
+      <x:c r="K6" s="50"/>
+      <x:c r="L6" s="50"/>
+    </x:row>
+    <x:row r="7" ht="42" customHeight="1">
+      <x:c r="A7" s="50"/>
+      <x:c r="B7" s="50"/>
+      <x:c r="C7" s="50"/>
+      <x:c r="D7" s="62"/>
+      <x:c r="E7" s="62"/>
+      <x:c r="F7" s="70"/>
+      <x:c r="G7" s="70"/>
+      <x:c r="H7" s="50"/>
+      <x:c r="I7" s="50"/>
+      <x:c r="J7" s="50"/>
+      <x:c r="K7" s="50"/>
+      <x:c r="L7" s="50"/>
+    </x:row>
+    <x:row r="8" ht="42" customHeight="1">
+      <x:c r="A8" s="50"/>
+      <x:c r="B8" s="50"/>
+      <x:c r="C8" s="50"/>
+      <x:c r="D8" s="62"/>
+      <x:c r="E8" s="62"/>
+      <x:c r="F8" s="70"/>
+      <x:c r="G8" s="70"/>
+      <x:c r="H8" s="50"/>
+      <x:c r="I8" s="50"/>
+      <x:c r="J8" s="50"/>
+      <x:c r="K8" s="50"/>
+      <x:c r="L8" s="50"/>
+    </x:row>
+    <x:row r="9" ht="42" customHeight="1">
+      <x:c r="A9" s="50"/>
+      <x:c r="B9" s="50"/>
+      <x:c r="C9" s="50"/>
+      <x:c r="D9" s="62"/>
+      <x:c r="E9" s="62"/>
+      <x:c r="F9" s="70"/>
+      <x:c r="G9" s="70"/>
+      <x:c r="H9" s="50"/>
+      <x:c r="I9" s="50"/>
+      <x:c r="J9" s="50"/>
+      <x:c r="K9" s="50"/>
+      <x:c r="L9" s="50"/>
+    </x:row>
+    <x:row r="10" ht="42" customHeight="1">
+      <x:c r="A10" s="50"/>
+      <x:c r="B10" s="50"/>
+      <x:c r="C10" s="50"/>
+      <x:c r="D10" s="62"/>
+      <x:c r="E10" s="62"/>
+      <x:c r="F10" s="70"/>
+      <x:c r="G10" s="70"/>
+      <x:c r="H10" s="50"/>
+      <x:c r="I10" s="50"/>
+      <x:c r="J10" s="50"/>
+      <x:c r="K10" s="50"/>
+      <x:c r="L10" s="50"/>
+    </x:row>
+    <x:row r="11" ht="42" customHeight="1">
+      <x:c r="A11" s="50"/>
+      <x:c r="B11" s="50"/>
+      <x:c r="C11" s="50"/>
+      <x:c r="D11" s="62"/>
+      <x:c r="E11" s="62"/>
+      <x:c r="F11" s="70"/>
+      <x:c r="G11" s="70"/>
+      <x:c r="H11" s="50"/>
+      <x:c r="I11" s="50"/>
+      <x:c r="J11" s="50"/>
+      <x:c r="K11" s="50"/>
+      <x:c r="L11" s="50"/>
+    </x:row>
+    <x:row r="12" ht="42" customHeight="1">
+      <x:c r="A12" s="50"/>
+      <x:c r="B12" s="50"/>
+      <x:c r="C12" s="50"/>
+      <x:c r="D12" s="62"/>
+      <x:c r="E12" s="62"/>
+      <x:c r="F12" s="70"/>
+      <x:c r="G12" s="70"/>
+      <x:c r="H12" s="50"/>
+      <x:c r="I12" s="50"/>
+      <x:c r="J12" s="50"/>
+      <x:c r="K12" s="50"/>
+      <x:c r="L12" s="50"/>
+    </x:row>
+    <x:row r="13" ht="42" customHeight="1">
+      <x:c r="A13" s="50"/>
+      <x:c r="B13" s="50"/>
+      <x:c r="C13" s="50"/>
+      <x:c r="D13" s="62"/>
+      <x:c r="E13" s="62"/>
+      <x:c r="F13" s="70"/>
+      <x:c r="G13" s="70"/>
+      <x:c r="H13" s="50"/>
+      <x:c r="I13" s="50"/>
+      <x:c r="J13" s="50"/>
+      <x:c r="K13" s="50"/>
+      <x:c r="L13" s="50"/>
+    </x:row>
+    <x:row r="14" ht="42" customHeight="1">
+      <x:c r="A14" s="50"/>
+      <x:c r="B14" s="50"/>
+      <x:c r="C14" s="50"/>
+      <x:c r="D14" s="62"/>
+      <x:c r="E14" s="62"/>
+      <x:c r="F14" s="70"/>
+      <x:c r="G14" s="70"/>
+      <x:c r="H14" s="50"/>
+      <x:c r="I14" s="50"/>
+      <x:c r="J14" s="50"/>
+      <x:c r="K14" s="50"/>
+      <x:c r="L14" s="50"/>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="115" t="str">
+        <x:v>Total coûts</x:v>
+      </x:c>
+      <x:c r="B16" s="115"/>
+      <x:c r="C16" s="115"/>
+      <x:c r="D16" s="115"/>
+      <x:c r="E16" s="115"/>
+      <x:c r="F16" s="115" t="n">
+        <x:f>SUM(F5:F14)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G16" s="115" t="n">
+        <x:f>SUM(G5:G14)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H16" s="115"/>
+      <x:c r="I16" s="115" t="str">
+        <x:v>Plafond pilote</x:v>
+      </x:c>
+      <x:c r="J16" s="116" t="n">
+        <x:v>8000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="115"/>
+      <x:c r="B17" s="115"/>
+      <x:c r="C17" s="115"/>
+      <x:c r="D17" s="115"/>
+      <x:c r="E17" s="115"/>
+      <x:c r="F17" s="115"/>
+      <x:c r="G17" s="115"/>
+      <x:c r="H17" s="115"/>
+      <x:c r="I17" s="115" t="str">
+        <x:v>Marge restante (réel)</x:v>
+      </x:c>
+      <x:c r="J17" s="116" t="n">
+        <x:f>J16-G16</x:f>
+        <x:v>8000</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:H1"/>
+    <x:mergeCell ref="A1:L1"/>
+    <x:mergeCell ref="A2:L2"/>
   </x:mergeCells>
-  <x:dataValidations count="1">
+  <x:dataValidations count="2">
     <x:dataValidation type="list" sqref="H4:H11">
       <x:formula1>"À faire,En cours,Bloqué,Terminé"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="K5:K14">
+      <x:formula1>"À faire,En cours,Bloquée,Terminée,À valider"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1c51edede121430d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8733a26302ac4037"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5749,72 +6623,170 @@
       <x:c r="D2" s="20"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="36" t="str">
+      <x:c r="A3" s="92" t="str">
         <x:v>Onglet</x:v>
       </x:c>
-      <x:c r="B3" s="36" t="str">
+      <x:c r="B3" s="92" t="str">
         <x:v>Situation</x:v>
       </x:c>
-      <x:c r="C3" s="36" t="str">
+      <x:c r="C3" s="92" t="str">
         <x:v>À quoi il sert</x:v>
       </x:c>
-      <x:c r="D3" s="36" t="str">
+      <x:c r="D3" s="92" t="str">
         <x:v>Attention</x:v>
       </x:c>
     </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="20" t="str">
+    <x:row r="4" ht="46" customHeight="1">
+      <x:c r="A4" s="50" t="str">
         <x:v>Fournisseurs_criticite</x:v>
       </x:c>
-      <x:c r="B4" s="20" t="str">
+      <x:c r="B4" s="50" t="str">
         <x:v>Situation 5</x:v>
       </x:c>
-      <x:c r="C4" s="20" t="str">
-        <x:v>Analyser dépendances, alternatives et délais de substitution.</x:v>
-      </x:c>
-      <x:c r="D4" s="20" t="str">
+      <x:c r="C4" s="50" t="str">
+        <x:v>Données sources sur les partenaires pédagogiques.</x:v>
+      </x:c>
+      <x:c r="D4" s="50" t="str">
         <x:v>Partenaires fictifs : ne rien attribuer aux partenaires réels de 1083.</x:v>
       </x:c>
     </x:row>
-    <x:row r="5">
-      <x:c r="A5" s="20" t="str">
+    <x:row r="5" ht="46" customHeight="1">
+      <x:c r="A5" s="50" t="str">
+        <x:v>Analyse_dependances</x:v>
+      </x:c>
+      <x:c r="B5" s="50" t="str">
+        <x:v>Situation 5</x:v>
+      </x:c>
+      <x:c r="C5" s="50" t="str">
+        <x:v>Analyser les dépendances et retenir trois priorités.</x:v>
+      </x:c>
+      <x:c r="D5" s="50" t="str">
+        <x:v>Ne transformez pas automatiquement chaque colonne en points ; justifiez votre méthode.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="46" customHeight="1">
+      <x:c r="A6" s="50" t="str">
+        <x:v>Veille_S5</x:v>
+      </x:c>
+      <x:c r="B6" s="50" t="str">
+        <x:v>Situation 5</x:v>
+      </x:c>
+      <x:c r="C6" s="50" t="str">
+        <x:v>Tracer l’actualisation de REP, coût environnemental et OFG.</x:v>
+      </x:c>
+      <x:c r="D6" s="50" t="str">
+        <x:v>« Aucune évolution identifiée » est un résultat valable si la vérification est datée et prouvée.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="46" customHeight="1">
+      <x:c r="A7" s="50" t="str">
+        <x:v>Projet_initial</x:v>
+      </x:c>
+      <x:c r="B7" s="50" t="str">
+        <x:v>Situation 5</x:v>
+      </x:c>
+      <x:c r="C7" s="50" t="str">
+        <x:v>Cadrer et planifier le mini-projet avant le diagnostic qualité détaillé.</x:v>
+      </x:c>
+      <x:c r="D7" s="50" t="str">
+        <x:v>Les actions qualité précises viennent après le diagnostic de la situation 6.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="46" customHeight="1">
+      <x:c r="A8" s="50" t="str">
+        <x:v>Retours_clients</x:v>
+      </x:c>
+      <x:c r="B8" s="50" t="str">
+        <x:v>Situation 6</x:v>
+      </x:c>
+      <x:c r="C8" s="50" t="str">
+        <x:v>Mesurer les dysfonctionnements et construire le premier Pareto.</x:v>
+      </x:c>
+      <x:c r="D8" s="50" t="str">
+        <x:v>Nombre brut ≠ taux ; Pareto ≠ preuve de cause.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="46" customHeight="1">
+      <x:c r="A9" s="50" t="str">
+        <x:v>Volumes_exposition</x:v>
+      </x:c>
+      <x:c r="B9" s="50" t="str">
+        <x:v>Situation 6</x:v>
+      </x:c>
+      <x:c r="C9" s="50" t="str">
+        <x:v>Fournir les dénominateurs nécessaires aux taux.</x:v>
+      </x:c>
+      <x:c r="D9" s="50" t="str">
+        <x:v>Les trois tableaux décrivent les mêmes unités sous trois angles : ne pas les additionner.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="46" customHeight="1">
+      <x:c r="A10" s="50" t="str">
+        <x:v>Diagnostic_complementaire</x:v>
+      </x:c>
+      <x:c r="B10" s="50" t="str">
+        <x:v>Situation 6</x:v>
+      </x:c>
+      <x:c r="C10" s="50" t="str">
+        <x:v>Tester les hypothèses par des preuves complémentaires.</x:v>
+      </x:c>
+      <x:c r="D10" s="50" t="str">
+        <x:v>Une convergence d’indices doit conduire à une conclusion proportionnée, pas à une certitude artificielle.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="46" customHeight="1">
+      <x:c r="A11" s="50" t="str">
         <x:v>Projet_actions</x:v>
       </x:c>
-      <x:c r="B5" s="20" t="str">
-        <x:v>Situations 5 et 6</x:v>
-      </x:c>
-      <x:c r="C5" s="20" t="str">
-        <x:v>Préparer puis suivre un mini-projet professionnel.</x:v>
-      </x:c>
-      <x:c r="D5" s="20" t="str">
-        <x:v>Ce planning du scénario n’est pas le Kanban utilisé par votre groupe pour organiser son propre travail.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6">
-      <x:c r="A6" s="20" t="str">
-        <x:v>Retours_clients</x:v>
-      </x:c>
-      <x:c r="B6" s="20" t="str">
+      <x:c r="B11" s="50" t="str">
         <x:v>Situation 6</x:v>
       </x:c>
-      <x:c r="C6" s="20" t="str">
-        <x:v>Mesurer les dysfonctionnements, prioriser puis rechercher les causes.</x:v>
-      </x:c>
-      <x:c r="D6" s="20" t="str">
-        <x:v>Un nombre élevé de retours ne prouve ni un taux élevé ni une cause.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7">
-      <x:c r="A7" s="20" t="str">
+      <x:c r="C11" s="50" t="str">
+        <x:v>Transformer le diagnostic en actions testables et suivre le budget.</x:v>
+      </x:c>
+      <x:c r="D11" s="50" t="str">
+        <x:v>Ne pas préremplir les solutions avant le diagnostic.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="46" customHeight="1">
+      <x:c r="A12" s="50" t="str">
+        <x:v>Suivi_pilote</x:v>
+      </x:c>
+      <x:c r="B12" s="50" t="str">
+        <x:v>Situation 6</x:v>
+      </x:c>
+      <x:c r="C12" s="50" t="str">
+        <x:v>Mesurer les résultats du pilote pendant quatre semaines.</x:v>
+      </x:c>
+      <x:c r="D12" s="50" t="str">
+        <x:v>Les retours clients peuvent arriver avec retard : prolonger le suivi si nécessaire.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="46" customHeight="1">
+      <x:c r="A13" s="50" t="str">
+        <x:v>Capitalisation_REX</x:v>
+      </x:c>
+      <x:c r="B13" s="50" t="str">
+        <x:v>Situation 6</x:v>
+      </x:c>
+      <x:c r="C13" s="50" t="str">
+        <x:v>Conserver les faits, décisions, preuves et limites pour réutilisation future.</x:v>
+      </x:c>
+      <x:c r="D13" s="50" t="str">
+        <x:v>Ce qui n’est pas démontré doit rester « à confirmer ».</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="46" customHeight="1">
+      <x:c r="A14" s="50" t="str">
         <x:v>Principe</x:v>
       </x:c>
-      <x:c r="B7" s="20" t="str">
+      <x:c r="B14" s="50" t="str">
         <x:v>Toutes</x:v>
       </x:c>
-      <x:c r="C7" s="20" t="str">
+      <x:c r="C14" s="50" t="str">
         <x:v>Contrôler les données avant d’interpréter.</x:v>
       </x:c>
-      <x:c r="D7" s="20" t="str">
+      <x:c r="D14" s="50" t="str">
         <x:v>Signalez les informations manquantes ; n’inventez pas.</x:v>
       </x:c>
     </x:row>
@@ -5824,4 +6796,1599 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="16" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="20" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="16" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="24" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="34" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="20" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="34" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="30" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="14" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="32" customHeight="1">
+      <x:c r="A1" s="44" t="str">
+        <x:v>SITUATION 5 — ANALYSE DES DÉPENDANCES FOURNISSEURS. Les données des partenaires A à J sont fictives.</x:v>
+      </x:c>
+      <x:c r="B1" s="44"/>
+      <x:c r="C1" s="44"/>
+      <x:c r="D1" s="44"/>
+      <x:c r="E1" s="44"/>
+      <x:c r="F1" s="44"/>
+      <x:c r="G1" s="44"/>
+      <x:c r="H1" s="44"/>
+      <x:c r="I1" s="44"/>
+      <x:c r="J1" s="44"/>
+      <x:c r="K1" s="44"/>
+      <x:c r="L1" s="44"/>
+    </x:row>
+    <x:row r="2" ht="54" customHeight="1">
+      <x:c r="A2" s="40" t="str">
+        <x:v>Évaluez plusieurs dimensions avant de conclure. Une priorité peut être forte même sans incident récent si l’alternative est absente, lente ou insuffisamment qualifiée. Si une information manque pour conclure, utilisez « NE » et précisez ce qu’il faut vérifier.</x:v>
+      </x:c>
+      <x:c r="B2" s="40"/>
+      <x:c r="C2" s="40"/>
+      <x:c r="D2" s="40"/>
+      <x:c r="E2" s="40"/>
+      <x:c r="F2" s="40"/>
+      <x:c r="G2" s="40"/>
+      <x:c r="H2" s="40"/>
+      <x:c r="I2" s="40"/>
+      <x:c r="J2" s="40"/>
+      <x:c r="K2" s="40"/>
+      <x:c r="L2" s="40"/>
+    </x:row>
+    <x:row r="4" ht="42" customHeight="1">
+      <x:c r="A4" s="49" t="str">
+        <x:v>Partenaire</x:v>
+      </x:c>
+      <x:c r="B4" s="49" t="str">
+        <x:v>Étape</x:v>
+      </x:c>
+      <x:c r="C4" s="49" t="str">
+        <x:v>Part des volumes</x:v>
+      </x:c>
+      <x:c r="D4" s="49" t="str">
+        <x:v>Alternative qualifiée ?</x:v>
+      </x:c>
+      <x:c r="E4" s="49" t="str">
+        <x:v>Délai de substitution</x:v>
+      </x:c>
+      <x:c r="F4" s="49" t="str">
+        <x:v>Dépendance technique</x:v>
+      </x:c>
+      <x:c r="G4" s="49" t="str">
+        <x:v>Incidents / signaux</x:v>
+      </x:c>
+      <x:c r="H4" s="49" t="str">
+        <x:v>Conséquence plausible sur la continuité</x:v>
+      </x:c>
+      <x:c r="I4" s="49" t="str">
+        <x:v>Niveau de dépendance retenu</x:v>
+      </x:c>
+      <x:c r="J4" s="49" t="str">
+        <x:v>Justification</x:v>
+      </x:c>
+      <x:c r="K4" s="49" t="str">
+        <x:v>Information à confirmer</x:v>
+      </x:c>
+      <x:c r="L4" s="49" t="str">
+        <x:v>Priorité ?</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="54" customHeight="1">
+      <x:c r="A5" s="50" t="str">
+        <x:f>Fournisseurs_criticite!A4</x:f>
+        <x:v>Partenaire A</x:v>
+      </x:c>
+      <x:c r="B5" s="50" t="str">
+        <x:f>Fournisseurs_criticite!B4</x:f>
+        <x:v>Filature coton</x:v>
+      </x:c>
+      <x:c r="C5" s="50" t="str">
+        <x:f>Fournisseurs_criticite!C4</x:f>
+        <x:v>42 %</x:v>
+      </x:c>
+      <x:c r="D5" s="50" t="str">
+        <x:f>Fournisseurs_criticite!E4</x:f>
+        <x:v>Oui</x:v>
+      </x:c>
+      <x:c r="E5" s="50" t="str">
+        <x:f>Fournisseurs_criticite!F4</x:f>
+        <x:v>6 sem.</x:v>
+      </x:c>
+      <x:c r="F5" s="50" t="str">
+        <x:f>Fournisseurs_criticite!G4</x:f>
+        <x:v>Moyenne</x:v>
+      </x:c>
+      <x:c r="G5" s="50" t="str">
+        <x:f>Fournisseurs_criticite!I4</x:f>
+        <x:v>1 retard de 5 jours</x:v>
+      </x:c>
+      <x:c r="H5" s="50"/>
+      <x:c r="I5" s="50"/>
+      <x:c r="J5" s="50"/>
+      <x:c r="K5" s="50"/>
+      <x:c r="L5" s="50"/>
+    </x:row>
+    <x:row r="6" ht="54" customHeight="1">
+      <x:c r="A6" s="50" t="str">
+        <x:f>Fournisseurs_criticite!A5</x:f>
+        <x:v>Partenaire B</x:v>
+      </x:c>
+      <x:c r="B6" s="50" t="str">
+        <x:f>Fournisseurs_criticite!B5</x:f>
+        <x:v>Filature recyclée</x:v>
+      </x:c>
+      <x:c r="C6" s="50" t="str">
+        <x:f>Fournisseurs_criticite!C5</x:f>
+        <x:v>31 %</x:v>
+      </x:c>
+      <x:c r="D6" s="50" t="str">
+        <x:f>Fournisseurs_criticite!E5</x:f>
+        <x:v>Non</x:v>
+      </x:c>
+      <x:c r="E6" s="50" t="str">
+        <x:f>Fournisseurs_criticite!F5</x:f>
+        <x:v>12 sem.</x:v>
+      </x:c>
+      <x:c r="F6" s="50" t="str">
+        <x:f>Fournisseurs_criticite!G5</x:f>
+        <x:v>Élevée</x:v>
+      </x:c>
+      <x:c r="G6" s="50" t="str">
+        <x:f>Fournisseurs_criticite!I5</x:f>
+        <x:v>Aucun</x:v>
+      </x:c>
+      <x:c r="H6" s="50"/>
+      <x:c r="I6" s="50"/>
+      <x:c r="J6" s="50"/>
+      <x:c r="K6" s="50"/>
+      <x:c r="L6" s="50"/>
+    </x:row>
+    <x:row r="7" ht="54" customHeight="1">
+      <x:c r="A7" s="50" t="str">
+        <x:f>Fournisseurs_criticite!A6</x:f>
+        <x:v>Partenaire C</x:v>
+      </x:c>
+      <x:c r="B7" s="50" t="str">
+        <x:f>Fournisseurs_criticite!B6</x:f>
+        <x:v>Teinture</x:v>
+      </x:c>
+      <x:c r="C7" s="50" t="str">
+        <x:f>Fournisseurs_criticite!C6</x:f>
+        <x:v>55 %</x:v>
+      </x:c>
+      <x:c r="D7" s="50" t="str">
+        <x:f>Fournisseurs_criticite!E6</x:f>
+        <x:v>Oui</x:v>
+      </x:c>
+      <x:c r="E7" s="50" t="str">
+        <x:f>Fournisseurs_criticite!F6</x:f>
+        <x:v>8 sem.</x:v>
+      </x:c>
+      <x:c r="F7" s="50" t="str">
+        <x:f>Fournisseurs_criticite!G6</x:f>
+        <x:v>Élevée</x:v>
+      </x:c>
+      <x:c r="G7" s="50" t="str">
+        <x:f>Fournisseurs_criticite!I6</x:f>
+        <x:v>1 panne de 3 jours</x:v>
+      </x:c>
+      <x:c r="H7" s="50"/>
+      <x:c r="I7" s="50"/>
+      <x:c r="J7" s="50"/>
+      <x:c r="K7" s="50"/>
+      <x:c r="L7" s="50"/>
+    </x:row>
+    <x:row r="8" ht="54" customHeight="1">
+      <x:c r="A8" s="50" t="str">
+        <x:f>Fournisseurs_criticite!A7</x:f>
+        <x:v>Partenaire D</x:v>
+      </x:c>
+      <x:c r="B8" s="50" t="str">
+        <x:f>Fournisseurs_criticite!B7</x:f>
+        <x:v>Tissage</x:v>
+      </x:c>
+      <x:c r="C8" s="50" t="str">
+        <x:f>Fournisseurs_criticite!C7</x:f>
+        <x:v>46 %</x:v>
+      </x:c>
+      <x:c r="D8" s="50" t="str">
+        <x:f>Fournisseurs_criticite!E7</x:f>
+        <x:v>Oui</x:v>
+      </x:c>
+      <x:c r="E8" s="50" t="str">
+        <x:f>Fournisseurs_criticite!F7</x:f>
+        <x:v>5 sem.</x:v>
+      </x:c>
+      <x:c r="F8" s="50" t="str">
+        <x:f>Fournisseurs_criticite!G7</x:f>
+        <x:v>Moyenne</x:v>
+      </x:c>
+      <x:c r="G8" s="50" t="str">
+        <x:f>Fournisseurs_criticite!I7</x:f>
+        <x:v>2 retards</x:v>
+      </x:c>
+      <x:c r="H8" s="50"/>
+      <x:c r="I8" s="50"/>
+      <x:c r="J8" s="50"/>
+      <x:c r="K8" s="50"/>
+      <x:c r="L8" s="50"/>
+    </x:row>
+    <x:row r="9" ht="54" customHeight="1">
+      <x:c r="A9" s="50" t="str">
+        <x:f>Fournisseurs_criticite!A8</x:f>
+        <x:v>Partenaire E</x:v>
+      </x:c>
+      <x:c r="B9" s="50" t="str">
+        <x:f>Fournisseurs_criticite!B8</x:f>
+        <x:v>Coupe</x:v>
+      </x:c>
+      <x:c r="C9" s="50" t="str">
+        <x:f>Fournisseurs_criticite!C8</x:f>
+        <x:v>38 %</x:v>
+      </x:c>
+      <x:c r="D9" s="50" t="str">
+        <x:f>Fournisseurs_criticite!E8</x:f>
+        <x:v>Non</x:v>
+      </x:c>
+      <x:c r="E9" s="50" t="str">
+        <x:f>Fournisseurs_criticite!F8</x:f>
+        <x:v>10 sem.</x:v>
+      </x:c>
+      <x:c r="F9" s="50" t="str">
+        <x:f>Fournisseurs_criticite!G8</x:f>
+        <x:v>Très élevée</x:v>
+      </x:c>
+      <x:c r="G9" s="50" t="str">
+        <x:f>Fournisseurs_criticite!I8</x:f>
+        <x:v>Arrêt machine 2 jours</x:v>
+      </x:c>
+      <x:c r="H9" s="50"/>
+      <x:c r="I9" s="50"/>
+      <x:c r="J9" s="50"/>
+      <x:c r="K9" s="50"/>
+      <x:c r="L9" s="50"/>
+    </x:row>
+    <x:row r="10" ht="54" customHeight="1">
+      <x:c r="A10" s="50" t="str">
+        <x:f>Fournisseurs_criticite!A9</x:f>
+        <x:v>Partenaire F</x:v>
+      </x:c>
+      <x:c r="B10" s="50" t="str">
+        <x:f>Fournisseurs_criticite!B9</x:f>
+        <x:v>Confection</x:v>
+      </x:c>
+      <x:c r="C10" s="50" t="str">
+        <x:f>Fournisseurs_criticite!C9</x:f>
+        <x:v>34 %</x:v>
+      </x:c>
+      <x:c r="D10" s="50" t="str">
+        <x:f>Fournisseurs_criticite!E9</x:f>
+        <x:v>Oui</x:v>
+      </x:c>
+      <x:c r="E10" s="50" t="str">
+        <x:f>Fournisseurs_criticite!F9</x:f>
+        <x:v>4 sem.</x:v>
+      </x:c>
+      <x:c r="F10" s="50" t="str">
+        <x:f>Fournisseurs_criticite!G9</x:f>
+        <x:v>Moyenne</x:v>
+      </x:c>
+      <x:c r="G10" s="50" t="str">
+        <x:f>Fournisseurs_criticite!I9</x:f>
+        <x:v>Hausse retouches</x:v>
+      </x:c>
+      <x:c r="H10" s="50"/>
+      <x:c r="I10" s="50"/>
+      <x:c r="J10" s="50"/>
+      <x:c r="K10" s="50"/>
+      <x:c r="L10" s="50"/>
+    </x:row>
+    <x:row r="11" ht="54" customHeight="1">
+      <x:c r="A11" s="50" t="str">
+        <x:f>Fournisseurs_criticite!A10</x:f>
+        <x:v>Partenaire G</x:v>
+      </x:c>
+      <x:c r="B11" s="50" t="str">
+        <x:f>Fournisseurs_criticite!B10</x:f>
+        <x:v>Confection</x:v>
+      </x:c>
+      <x:c r="C11" s="50" t="str">
+        <x:f>Fournisseurs_criticite!C10</x:f>
+        <x:v>22 %</x:v>
+      </x:c>
+      <x:c r="D11" s="50" t="str">
+        <x:f>Fournisseurs_criticite!E10</x:f>
+        <x:v>Oui</x:v>
+      </x:c>
+      <x:c r="E11" s="50" t="str">
+        <x:f>Fournisseurs_criticite!F10</x:f>
+        <x:v>5 sem.</x:v>
+      </x:c>
+      <x:c r="F11" s="50" t="str">
+        <x:f>Fournisseurs_criticite!G10</x:f>
+        <x:v>Faible</x:v>
+      </x:c>
+      <x:c r="G11" s="50" t="str">
+        <x:f>Fournisseurs_criticite!I10</x:f>
+        <x:v>Aucun</x:v>
+      </x:c>
+      <x:c r="H11" s="50"/>
+      <x:c r="I11" s="50"/>
+      <x:c r="J11" s="50"/>
+      <x:c r="K11" s="50"/>
+      <x:c r="L11" s="50"/>
+    </x:row>
+    <x:row r="12" ht="54" customHeight="1">
+      <x:c r="A12" s="50" t="str">
+        <x:f>Fournisseurs_criticite!A11</x:f>
+        <x:v>Partenaire H</x:v>
+      </x:c>
+      <x:c r="B12" s="50" t="str">
+        <x:f>Fournisseurs_criticite!B11</x:f>
+        <x:v>Accessoires métalliques</x:v>
+      </x:c>
+      <x:c r="C12" s="50" t="str">
+        <x:f>Fournisseurs_criticite!C11</x:f>
+        <x:v>62 %</x:v>
+      </x:c>
+      <x:c r="D12" s="50" t="str">
+        <x:f>Fournisseurs_criticite!E11</x:f>
+        <x:v>Non</x:v>
+      </x:c>
+      <x:c r="E12" s="50" t="str">
+        <x:f>Fournisseurs_criticite!F11</x:f>
+        <x:v>14 sem.</x:v>
+      </x:c>
+      <x:c r="F12" s="50" t="str">
+        <x:f>Fournisseurs_criticite!G11</x:f>
+        <x:v>Élevée</x:v>
+      </x:c>
+      <x:c r="G12" s="50" t="str">
+        <x:f>Fournisseurs_criticite!I11</x:f>
+        <x:v>Retard transport</x:v>
+      </x:c>
+      <x:c r="H12" s="50"/>
+      <x:c r="I12" s="50"/>
+      <x:c r="J12" s="50"/>
+      <x:c r="K12" s="50"/>
+      <x:c r="L12" s="50"/>
+    </x:row>
+    <x:row r="13" ht="54" customHeight="1">
+      <x:c r="A13" s="50" t="str">
+        <x:f>Fournisseurs_criticite!A12</x:f>
+        <x:v>Partenaire I</x:v>
+      </x:c>
+      <x:c r="B13" s="50" t="str">
+        <x:f>Fournisseurs_criticite!B12</x:f>
+        <x:v>Cartons d'expédition</x:v>
+      </x:c>
+      <x:c r="C13" s="50" t="str">
+        <x:f>Fournisseurs_criticite!C12</x:f>
+        <x:v>70 %</x:v>
+      </x:c>
+      <x:c r="D13" s="50" t="str">
+        <x:f>Fournisseurs_criticite!E12</x:f>
+        <x:v>Oui</x:v>
+      </x:c>
+      <x:c r="E13" s="50" t="str">
+        <x:f>Fournisseurs_criticite!F12</x:f>
+        <x:v>2 sem.</x:v>
+      </x:c>
+      <x:c r="F13" s="50" t="str">
+        <x:f>Fournisseurs_criticite!G12</x:f>
+        <x:v>Faible</x:v>
+      </x:c>
+      <x:c r="G13" s="50" t="str">
+        <x:f>Fournisseurs_criticite!I12</x:f>
+        <x:v>Aucun</x:v>
+      </x:c>
+      <x:c r="H13" s="50"/>
+      <x:c r="I13" s="50"/>
+      <x:c r="J13" s="50"/>
+      <x:c r="K13" s="50"/>
+      <x:c r="L13" s="50"/>
+    </x:row>
+    <x:row r="14" ht="54" customHeight="1">
+      <x:c r="A14" s="50" t="str">
+        <x:f>Fournisseurs_criticite!A13</x:f>
+        <x:v>Partenaire J</x:v>
+      </x:c>
+      <x:c r="B14" s="50" t="str">
+        <x:f>Fournisseurs_criticite!B13</x:f>
+        <x:v>Transport B2B</x:v>
+      </x:c>
+      <x:c r="C14" s="50" t="str">
+        <x:f>Fournisseurs_criticite!C13</x:f>
+        <x:v>51 %</x:v>
+      </x:c>
+      <x:c r="D14" s="50" t="str">
+        <x:f>Fournisseurs_criticite!E13</x:f>
+        <x:v>Oui</x:v>
+      </x:c>
+      <x:c r="E14" s="50" t="str">
+        <x:f>Fournisseurs_criticite!F13</x:f>
+        <x:v>1 sem.</x:v>
+      </x:c>
+      <x:c r="F14" s="50" t="str">
+        <x:f>Fournisseurs_criticite!G13</x:f>
+        <x:v>Faible</x:v>
+      </x:c>
+      <x:c r="G14" s="50" t="str">
+        <x:f>Fournisseurs_criticite!I13</x:f>
+        <x:v>2 incidents livraison</x:v>
+      </x:c>
+      <x:c r="H14" s="50"/>
+      <x:c r="I14" s="50"/>
+      <x:c r="J14" s="50"/>
+      <x:c r="K14" s="50"/>
+      <x:c r="L14" s="50"/>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:L1"/>
+    <x:mergeCell ref="A2:L2"/>
+  </x:mergeCells>
+  <x:dataValidations count="2">
+    <x:dataValidation type="list" sqref="I5:I14">
+      <x:formula1>"Faible,Modérée,Forte,Critique,NE"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="L5:L14">
+      <x:formula1>"Oui,Non,À confirmer"</x:formula1>
+    </x:dataValidation>
+  </x:dataValidations>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="28" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="28" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="34" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="34" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="34" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="30" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="24" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="20" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="32" customHeight="1">
+      <x:c r="A1" s="44" t="str">
+        <x:v>SITUATION 5 — MISE À JOUR DE VEILLE. Vérifiez les sources officielles indiquées dans R09 et datez chaque consultation.</x:v>
+      </x:c>
+      <x:c r="B1" s="44"/>
+      <x:c r="C1" s="44"/>
+      <x:c r="D1" s="44"/>
+      <x:c r="E1" s="44"/>
+      <x:c r="F1" s="44"/>
+      <x:c r="G1" s="44"/>
+      <x:c r="H1" s="44"/>
+      <x:c r="I1" s="44"/>
+      <x:c r="J1" s="44"/>
+    </x:row>
+    <x:row r="2" ht="42" customHeight="1">
+      <x:c r="A2" s="54" t="str">
+        <x:v>Une veille peut conclure à « aucune évolution identifiée » : l’essentiel est d’avoir vérifié la source, conservé une preuve et déterminé si une décision ou une alerte est nécessaire.</x:v>
+      </x:c>
+      <x:c r="B2" s="54"/>
+      <x:c r="C2" s="54"/>
+      <x:c r="D2" s="54"/>
+      <x:c r="E2" s="54"/>
+      <x:c r="F2" s="54"/>
+      <x:c r="G2" s="54"/>
+      <x:c r="H2" s="54"/>
+      <x:c r="I2" s="54"/>
+      <x:c r="J2" s="54"/>
+    </x:row>
+    <x:row r="4" ht="44" customHeight="1">
+      <x:c r="A4" s="49" t="str">
+        <x:v>Sujet</x:v>
+      </x:c>
+      <x:c r="B4" s="49" t="str">
+        <x:v>Point de départ R09</x:v>
+      </x:c>
+      <x:c r="C4" s="49" t="str">
+        <x:v>Source actuelle consultée</x:v>
+      </x:c>
+      <x:c r="D4" s="49" t="str">
+        <x:v>Date de consultation</x:v>
+      </x:c>
+      <x:c r="E4" s="49" t="str">
+        <x:v>Statut / règle actuelle</x:v>
+      </x:c>
+      <x:c r="F4" s="49" t="str">
+        <x:v>Évolution identifiée ?</x:v>
+      </x:c>
+      <x:c r="G4" s="49" t="str">
+        <x:v>Conséquence pour la PME</x:v>
+      </x:c>
+      <x:c r="H4" s="49" t="str">
+        <x:v>Preuve à conserver</x:v>
+      </x:c>
+      <x:c r="I4" s="49" t="str">
+        <x:v>Personne à alerter</x:v>
+      </x:c>
+      <x:c r="J4" s="49" t="str">
+        <x:v>Prochaine vérification</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="64" customHeight="1">
+      <x:c r="A5" s="50" t="str">
+        <x:v>REP textiles / TLC</x:v>
+      </x:c>
+      <x:c r="B5" s="50" t="str">
+        <x:v>Voir R09 — point de départ vérifié le 20/09/2026</x:v>
+      </x:c>
+      <x:c r="C5" s="50"/>
+      <x:c r="D5" s="50"/>
+      <x:c r="E5" s="50"/>
+      <x:c r="F5" s="50"/>
+      <x:c r="G5" s="50"/>
+      <x:c r="H5" s="50"/>
+      <x:c r="I5" s="50"/>
+      <x:c r="J5" s="50"/>
+    </x:row>
+    <x:row r="6" ht="64" customHeight="1">
+      <x:c r="A6" s="50" t="str">
+        <x:v>Affichage du coût environnemental des vêtements</x:v>
+      </x:c>
+      <x:c r="B6" s="50" t="str">
+        <x:v>Voir R09 — point de départ vérifié le 20/09/2026</x:v>
+      </x:c>
+      <x:c r="C6" s="50"/>
+      <x:c r="D6" s="50"/>
+      <x:c r="E6" s="50"/>
+      <x:c r="F6" s="50"/>
+      <x:c r="G6" s="50"/>
+      <x:c r="H6" s="50"/>
+      <x:c r="I6" s="50"/>
+      <x:c r="J6" s="50"/>
+    </x:row>
+    <x:row r="7" ht="64" customHeight="1">
+      <x:c r="A7" s="50" t="str">
+        <x:v>Origine France Garantie (OFG)</x:v>
+      </x:c>
+      <x:c r="B7" s="50" t="str">
+        <x:v>Voir R09 — point de départ vérifié le 20/09/2026</x:v>
+      </x:c>
+      <x:c r="C7" s="50"/>
+      <x:c r="D7" s="50"/>
+      <x:c r="E7" s="50"/>
+      <x:c r="F7" s="50"/>
+      <x:c r="G7" s="50"/>
+      <x:c r="H7" s="50"/>
+      <x:c r="I7" s="50"/>
+      <x:c r="J7" s="50"/>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:J1"/>
+    <x:mergeCell ref="A2:J2"/>
+  </x:mergeCells>
+  <x:dataValidations count="1">
+    <x:dataValidation type="list" sqref="F5:F7">
+      <x:formula1>"Oui,Non,À confirmer"</x:formula1>
+    </x:dataValidation>
+  </x:dataValidations>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="13" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="16" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="15" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="15" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="22" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="24" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="16" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="14" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="28" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="24" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="32" customHeight="1">
+      <x:c r="A1" s="44" t="str">
+        <x:v>SITUATION 5 — CADRAGE ET PLANNING INITIAL DU MINI-PROJET</x:v>
+      </x:c>
+      <x:c r="B1" s="44"/>
+      <x:c r="C1" s="44"/>
+      <x:c r="D1" s="44"/>
+      <x:c r="E1" s="44"/>
+      <x:c r="F1" s="44"/>
+      <x:c r="G1" s="44"/>
+      <x:c r="H1" s="44"/>
+      <x:c r="I1" s="44"/>
+      <x:c r="J1" s="44"/>
+      <x:c r="K1" s="44"/>
+    </x:row>
+    <x:row r="2" ht="54" customHeight="1">
+      <x:c r="A2" s="40" t="str">
+        <x:v>Planifiez ce qui est justifiable avec les informations disponibles. Pour le volet qualité, le diagnostic détaillé sera réalisé en situation 6 : prévoyez un lot de diagnostic et un jalon de décision, sans inventer dès maintenant des causes ou des actions correctrices.</x:v>
+      </x:c>
+      <x:c r="B2" s="40"/>
+      <x:c r="C2" s="40"/>
+      <x:c r="D2" s="40"/>
+      <x:c r="E2" s="40"/>
+      <x:c r="F2" s="40"/>
+      <x:c r="G2" s="40"/>
+      <x:c r="H2" s="40"/>
+      <x:c r="I2" s="40"/>
+      <x:c r="J2" s="40"/>
+      <x:c r="K2" s="40"/>
+    </x:row>
+    <x:row r="4" ht="36" customHeight="1">
+      <x:c r="A4" s="58" t="str">
+        <x:v>Besoin / problème à traiter</x:v>
+      </x:c>
+      <x:c r="B4" s="61"/>
+      <x:c r="C4" s="61"/>
+      <x:c r="D4" s="61"/>
+      <x:c r="E4" s="61"/>
+      <x:c r="F4" s="61"/>
+      <x:c r="G4" s="61"/>
+      <x:c r="H4" s="61"/>
+      <x:c r="I4" s="61"/>
+      <x:c r="J4" s="61"/>
+      <x:c r="K4" s="61"/>
+    </x:row>
+    <x:row r="5" ht="36" customHeight="1">
+      <x:c r="A5" s="58" t="str">
+        <x:v>Objectif SMART</x:v>
+      </x:c>
+      <x:c r="B5" s="61"/>
+      <x:c r="C5" s="61"/>
+      <x:c r="D5" s="61"/>
+      <x:c r="E5" s="61"/>
+      <x:c r="F5" s="61"/>
+      <x:c r="G5" s="61"/>
+      <x:c r="H5" s="61"/>
+      <x:c r="I5" s="61"/>
+      <x:c r="J5" s="61"/>
+      <x:c r="K5" s="61"/>
+    </x:row>
+    <x:row r="6" ht="36" customHeight="1">
+      <x:c r="A6" s="58" t="str">
+        <x:v>Périmètre inclus</x:v>
+      </x:c>
+      <x:c r="B6" s="61"/>
+      <x:c r="C6" s="61"/>
+      <x:c r="D6" s="61"/>
+      <x:c r="E6" s="61"/>
+      <x:c r="F6" s="61"/>
+      <x:c r="G6" s="61"/>
+      <x:c r="H6" s="61"/>
+      <x:c r="I6" s="61"/>
+      <x:c r="J6" s="61"/>
+      <x:c r="K6" s="61"/>
+    </x:row>
+    <x:row r="7" ht="36" customHeight="1">
+      <x:c r="A7" s="58" t="str">
+        <x:v>Périmètre exclu / différé</x:v>
+      </x:c>
+      <x:c r="B7" s="61"/>
+      <x:c r="C7" s="61"/>
+      <x:c r="D7" s="61"/>
+      <x:c r="E7" s="61"/>
+      <x:c r="F7" s="61"/>
+      <x:c r="G7" s="61"/>
+      <x:c r="H7" s="61"/>
+      <x:c r="I7" s="61"/>
+      <x:c r="J7" s="61"/>
+      <x:c r="K7" s="61"/>
+    </x:row>
+    <x:row r="8" ht="36" customHeight="1">
+      <x:c r="A8" s="58" t="str">
+        <x:v>Commanditaire</x:v>
+      </x:c>
+      <x:c r="B8" s="61"/>
+      <x:c r="C8" s="61"/>
+      <x:c r="D8" s="61"/>
+      <x:c r="E8" s="61"/>
+      <x:c r="F8" s="61"/>
+      <x:c r="G8" s="61"/>
+      <x:c r="H8" s="61"/>
+      <x:c r="I8" s="61"/>
+      <x:c r="J8" s="61"/>
+      <x:c r="K8" s="61"/>
+    </x:row>
+    <x:row r="9" ht="36" customHeight="1">
+      <x:c r="A9" s="58" t="str">
+        <x:v>Acteurs à mobiliser</x:v>
+      </x:c>
+      <x:c r="B9" s="61"/>
+      <x:c r="C9" s="61"/>
+      <x:c r="D9" s="61"/>
+      <x:c r="E9" s="61"/>
+      <x:c r="F9" s="61"/>
+      <x:c r="G9" s="61"/>
+      <x:c r="H9" s="61"/>
+      <x:c r="I9" s="61"/>
+      <x:c r="J9" s="61"/>
+      <x:c r="K9" s="61"/>
+    </x:row>
+    <x:row r="10" ht="36" customHeight="1">
+      <x:c r="A10" s="58" t="str">
+        <x:v>Contraintes principales</x:v>
+      </x:c>
+      <x:c r="B10" s="61"/>
+      <x:c r="C10" s="61"/>
+      <x:c r="D10" s="61"/>
+      <x:c r="E10" s="61"/>
+      <x:c r="F10" s="61"/>
+      <x:c r="G10" s="61"/>
+      <x:c r="H10" s="61"/>
+      <x:c r="I10" s="61"/>
+      <x:c r="J10" s="61"/>
+      <x:c r="K10" s="61"/>
+    </x:row>
+    <x:row r="11" ht="36" customHeight="1">
+      <x:c r="A11" s="58" t="str">
+        <x:v>Livrables attendus</x:v>
+      </x:c>
+      <x:c r="B11" s="61"/>
+      <x:c r="C11" s="61"/>
+      <x:c r="D11" s="61"/>
+      <x:c r="E11" s="61"/>
+      <x:c r="F11" s="61"/>
+      <x:c r="G11" s="61"/>
+      <x:c r="H11" s="61"/>
+      <x:c r="I11" s="61"/>
+      <x:c r="J11" s="61"/>
+      <x:c r="K11" s="61"/>
+    </x:row>
+    <x:row r="12" ht="36" customHeight="1">
+      <x:c r="A12" s="58" t="str">
+        <x:v>Critères de réussite</x:v>
+      </x:c>
+      <x:c r="B12" s="61"/>
+      <x:c r="C12" s="61"/>
+      <x:c r="D12" s="61"/>
+      <x:c r="E12" s="61"/>
+      <x:c r="F12" s="61"/>
+      <x:c r="G12" s="61"/>
+      <x:c r="H12" s="61"/>
+      <x:c r="I12" s="61"/>
+      <x:c r="J12" s="61"/>
+      <x:c r="K12" s="61"/>
+    </x:row>
+    <x:row r="13" ht="36" customHeight="1">
+      <x:c r="A13" s="58" t="str">
+        <x:v>Principaux risques du projet</x:v>
+      </x:c>
+      <x:c r="B13" s="61"/>
+      <x:c r="C13" s="61"/>
+      <x:c r="D13" s="61"/>
+      <x:c r="E13" s="61"/>
+      <x:c r="F13" s="61"/>
+      <x:c r="G13" s="61"/>
+      <x:c r="H13" s="61"/>
+      <x:c r="I13" s="61"/>
+      <x:c r="J13" s="61"/>
+      <x:c r="K13" s="61"/>
+    </x:row>
+    <x:row r="14" ht="36" customHeight="1">
+      <x:c r="A14" s="58" t="str">
+        <x:v>Réunion de lancement — objectif / participants</x:v>
+      </x:c>
+      <x:c r="B14" s="61"/>
+      <x:c r="C14" s="61"/>
+      <x:c r="D14" s="61"/>
+      <x:c r="E14" s="61"/>
+      <x:c r="F14" s="61"/>
+      <x:c r="G14" s="61"/>
+      <x:c r="H14" s="61"/>
+      <x:c r="I14" s="61"/>
+      <x:c r="J14" s="61"/>
+      <x:c r="K14" s="61"/>
+    </x:row>
+    <x:row r="17" ht="44" customHeight="1">
+      <x:c r="A17" s="79" t="str">
+        <x:v>Lot / tâche</x:v>
+      </x:c>
+      <x:c r="B17" s="79" t="str">
+        <x:v>Livrable / résultat</x:v>
+      </x:c>
+      <x:c r="C17" s="79" t="str">
+        <x:v>Responsable</x:v>
+      </x:c>
+      <x:c r="D17" s="79" t="str">
+        <x:v>Durée (jours)</x:v>
+      </x:c>
+      <x:c r="E17" s="79" t="str">
+        <x:v>Prédécesseur</x:v>
+      </x:c>
+      <x:c r="F17" s="79" t="str">
+        <x:v>Début prévu</x:v>
+      </x:c>
+      <x:c r="G17" s="79" t="str">
+        <x:v>Fin prévue</x:v>
+      </x:c>
+      <x:c r="H17" s="79" t="str">
+        <x:v>Jalon / validation</x:v>
+      </x:c>
+      <x:c r="I17" s="79" t="str">
+        <x:v>Indicateur / preuve</x:v>
+      </x:c>
+      <x:c r="J17" s="79" t="str">
+        <x:v>Coût estimé (€)</x:v>
+      </x:c>
+      <x:c r="K17" s="79" t="str">
+        <x:v>Statut</x:v>
+      </x:c>
+      <x:c r="L17" s="79" t="str">
+        <x:v>Risque projet / point de vigilance</x:v>
+      </x:c>
+      <x:c r="M17" s="79" t="str">
+        <x:v>Décision / arbitrage</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="44" customHeight="1">
+      <x:c r="A18" s="50"/>
+      <x:c r="B18" s="50"/>
+      <x:c r="C18" s="50"/>
+      <x:c r="D18" s="50"/>
+      <x:c r="E18" s="50"/>
+      <x:c r="F18" s="62"/>
+      <x:c r="G18" s="62" t="str">
+        <x:f>IF(OR(F18="",D18=""),"",F18+D18-1)</x:f>
+      </x:c>
+      <x:c r="H18" s="50"/>
+      <x:c r="I18" s="50"/>
+      <x:c r="J18" s="70"/>
+      <x:c r="K18" s="50"/>
+      <x:c r="L18" s="50"/>
+      <x:c r="M18" s="50"/>
+    </x:row>
+    <x:row r="19" ht="44" customHeight="1">
+      <x:c r="A19" s="50"/>
+      <x:c r="B19" s="50"/>
+      <x:c r="C19" s="50"/>
+      <x:c r="D19" s="50"/>
+      <x:c r="E19" s="50"/>
+      <x:c r="F19" s="62"/>
+      <x:c r="G19" s="62" t="str">
+        <x:f>IF(OR(F19="",D19=""),"",F19+D19-1)</x:f>
+      </x:c>
+      <x:c r="H19" s="50"/>
+      <x:c r="I19" s="50"/>
+      <x:c r="J19" s="70"/>
+      <x:c r="K19" s="50"/>
+      <x:c r="L19" s="50"/>
+      <x:c r="M19" s="50"/>
+    </x:row>
+    <x:row r="20" ht="44" customHeight="1">
+      <x:c r="A20" s="50"/>
+      <x:c r="B20" s="50"/>
+      <x:c r="C20" s="50"/>
+      <x:c r="D20" s="50"/>
+      <x:c r="E20" s="50"/>
+      <x:c r="F20" s="62"/>
+      <x:c r="G20" s="62" t="str">
+        <x:f>IF(OR(F20="",D20=""),"",F20+D20-1)</x:f>
+      </x:c>
+      <x:c r="H20" s="50"/>
+      <x:c r="I20" s="50"/>
+      <x:c r="J20" s="70"/>
+      <x:c r="K20" s="50"/>
+      <x:c r="L20" s="50"/>
+      <x:c r="M20" s="50"/>
+    </x:row>
+    <x:row r="21" ht="44" customHeight="1">
+      <x:c r="A21" s="50"/>
+      <x:c r="B21" s="50"/>
+      <x:c r="C21" s="50"/>
+      <x:c r="D21" s="50"/>
+      <x:c r="E21" s="50"/>
+      <x:c r="F21" s="62"/>
+      <x:c r="G21" s="62" t="str">
+        <x:f>IF(OR(F21="",D21=""),"",F21+D21-1)</x:f>
+      </x:c>
+      <x:c r="H21" s="50"/>
+      <x:c r="I21" s="50"/>
+      <x:c r="J21" s="70"/>
+      <x:c r="K21" s="50"/>
+      <x:c r="L21" s="50"/>
+      <x:c r="M21" s="50"/>
+    </x:row>
+    <x:row r="22" ht="44" customHeight="1">
+      <x:c r="A22" s="50"/>
+      <x:c r="B22" s="50"/>
+      <x:c r="C22" s="50"/>
+      <x:c r="D22" s="50"/>
+      <x:c r="E22" s="50"/>
+      <x:c r="F22" s="62"/>
+      <x:c r="G22" s="62" t="str">
+        <x:f>IF(OR(F22="",D22=""),"",F22+D22-1)</x:f>
+      </x:c>
+      <x:c r="H22" s="50"/>
+      <x:c r="I22" s="50"/>
+      <x:c r="J22" s="70"/>
+      <x:c r="K22" s="50"/>
+      <x:c r="L22" s="50"/>
+      <x:c r="M22" s="50"/>
+    </x:row>
+    <x:row r="23" ht="44" customHeight="1">
+      <x:c r="A23" s="50"/>
+      <x:c r="B23" s="50"/>
+      <x:c r="C23" s="50"/>
+      <x:c r="D23" s="50"/>
+      <x:c r="E23" s="50"/>
+      <x:c r="F23" s="62"/>
+      <x:c r="G23" s="62" t="str">
+        <x:f>IF(OR(F23="",D23=""),"",F23+D23-1)</x:f>
+      </x:c>
+      <x:c r="H23" s="50"/>
+      <x:c r="I23" s="50"/>
+      <x:c r="J23" s="70"/>
+      <x:c r="K23" s="50"/>
+      <x:c r="L23" s="50"/>
+      <x:c r="M23" s="50"/>
+    </x:row>
+    <x:row r="24" ht="44" customHeight="1">
+      <x:c r="A24" s="50"/>
+      <x:c r="B24" s="50"/>
+      <x:c r="C24" s="50"/>
+      <x:c r="D24" s="50"/>
+      <x:c r="E24" s="50"/>
+      <x:c r="F24" s="62"/>
+      <x:c r="G24" s="62" t="str">
+        <x:f>IF(OR(F24="",D24=""),"",F24+D24-1)</x:f>
+      </x:c>
+      <x:c r="H24" s="50"/>
+      <x:c r="I24" s="50"/>
+      <x:c r="J24" s="70"/>
+      <x:c r="K24" s="50"/>
+      <x:c r="L24" s="50"/>
+      <x:c r="M24" s="50"/>
+    </x:row>
+    <x:row r="25" ht="44" customHeight="1">
+      <x:c r="A25" s="50"/>
+      <x:c r="B25" s="50"/>
+      <x:c r="C25" s="50"/>
+      <x:c r="D25" s="50"/>
+      <x:c r="E25" s="50"/>
+      <x:c r="F25" s="62"/>
+      <x:c r="G25" s="62" t="str">
+        <x:f>IF(OR(F25="",D25=""),"",F25+D25-1)</x:f>
+      </x:c>
+      <x:c r="H25" s="50"/>
+      <x:c r="I25" s="50"/>
+      <x:c r="J25" s="70"/>
+      <x:c r="K25" s="50"/>
+      <x:c r="L25" s="50"/>
+      <x:c r="M25" s="50"/>
+    </x:row>
+    <x:row r="26" ht="44" customHeight="1">
+      <x:c r="A26" s="50"/>
+      <x:c r="B26" s="50"/>
+      <x:c r="C26" s="50"/>
+      <x:c r="D26" s="50"/>
+      <x:c r="E26" s="50"/>
+      <x:c r="F26" s="62"/>
+      <x:c r="G26" s="62" t="str">
+        <x:f>IF(OR(F26="",D26=""),"",F26+D26-1)</x:f>
+      </x:c>
+      <x:c r="H26" s="50"/>
+      <x:c r="I26" s="50"/>
+      <x:c r="J26" s="70"/>
+      <x:c r="K26" s="50"/>
+      <x:c r="L26" s="50"/>
+      <x:c r="M26" s="50"/>
+    </x:row>
+    <x:row r="27" ht="44" customHeight="1">
+      <x:c r="A27" s="50"/>
+      <x:c r="B27" s="50"/>
+      <x:c r="C27" s="50"/>
+      <x:c r="D27" s="50"/>
+      <x:c r="E27" s="50"/>
+      <x:c r="F27" s="62"/>
+      <x:c r="G27" s="62" t="str">
+        <x:f>IF(OR(F27="",D27=""),"",F27+D27-1)</x:f>
+      </x:c>
+      <x:c r="H27" s="50"/>
+      <x:c r="I27" s="50"/>
+      <x:c r="J27" s="70"/>
+      <x:c r="K27" s="50"/>
+      <x:c r="L27" s="50"/>
+      <x:c r="M27" s="50"/>
+    </x:row>
+    <x:row r="28" ht="44" customHeight="1">
+      <x:c r="A28" s="50"/>
+      <x:c r="B28" s="50"/>
+      <x:c r="C28" s="50"/>
+      <x:c r="D28" s="50"/>
+      <x:c r="E28" s="50"/>
+      <x:c r="F28" s="62"/>
+      <x:c r="G28" s="62" t="str">
+        <x:f>IF(OR(F28="",D28=""),"",F28+D28-1)</x:f>
+      </x:c>
+      <x:c r="H28" s="50"/>
+      <x:c r="I28" s="50"/>
+      <x:c r="J28" s="70"/>
+      <x:c r="K28" s="50"/>
+      <x:c r="L28" s="50"/>
+      <x:c r="M28" s="50"/>
+    </x:row>
+    <x:row r="29" ht="44" customHeight="1">
+      <x:c r="A29" s="50"/>
+      <x:c r="B29" s="50"/>
+      <x:c r="C29" s="50"/>
+      <x:c r="D29" s="50"/>
+      <x:c r="E29" s="50"/>
+      <x:c r="F29" s="62"/>
+      <x:c r="G29" s="62" t="str">
+        <x:f>IF(OR(F29="",D29=""),"",F29+D29-1)</x:f>
+      </x:c>
+      <x:c r="H29" s="50"/>
+      <x:c r="I29" s="50"/>
+      <x:c r="J29" s="70"/>
+      <x:c r="K29" s="50"/>
+      <x:c r="L29" s="50"/>
+      <x:c r="M29" s="50"/>
+    </x:row>
+    <x:row r="31">
+      <x:c r="I31" s="77" t="str">
+        <x:v>Total budget estimé</x:v>
+      </x:c>
+      <x:c r="J31" s="78" t="n">
+        <x:f>SUM(J18:J29)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K31" s="77" t="str">
+        <x:v>Plafond pilote</x:v>
+      </x:c>
+      <x:c r="L31" s="78" t="n">
+        <x:v>8000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32">
+      <x:c r="I32" s="77" t="str">
+        <x:v>Écart au plafond</x:v>
+      </x:c>
+      <x:c r="J32" s="78" t="n">
+        <x:f>L31-J31</x:f>
+        <x:v>8000</x:v>
+      </x:c>
+      <x:c r="K32" s="77"/>
+      <x:c r="L32" s="77"/>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:L1"/>
+    <x:mergeCell ref="A2:L2"/>
+    <x:mergeCell ref="B4:L4"/>
+    <x:mergeCell ref="B5:L5"/>
+    <x:mergeCell ref="B6:L6"/>
+    <x:mergeCell ref="B7:L7"/>
+    <x:mergeCell ref="B8:L8"/>
+    <x:mergeCell ref="B9:L9"/>
+    <x:mergeCell ref="B10:L10"/>
+    <x:mergeCell ref="B11:L11"/>
+    <x:mergeCell ref="B12:L12"/>
+    <x:mergeCell ref="B13:L13"/>
+    <x:mergeCell ref="B14:L14"/>
+  </x:mergeCells>
+  <x:dataValidations count="2">
+    <x:dataValidation type="list" sqref="J18:J29">
+      <x:formula1>"À faire,En cours,Bloquée,Terminée,À valider"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="K18:K29">
+      <x:formula1>"À faire,En cours,Bloquée,Terminée,À valider"</x:formula1>
+    </x:dataValidation>
+  </x:dataValidations>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="28" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="14" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="14" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="14" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="14" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="42" customHeight="1">
+      <x:c r="A1" s="95" t="str">
+        <x:v>SITUATION 6 — VOLUMES D’EXPOSITION. Données fictives créées pour permettre le calcul de taux.</x:v>
+      </x:c>
+      <x:c r="B1" s="95"/>
+      <x:c r="C1" s="95"/>
+      <x:c r="D1" s="95"/>
+      <x:c r="E1" s="95"/>
+      <x:c r="F1" s="95"/>
+      <x:c r="G1" s="95"/>
+      <x:c r="H1" s="95"/>
+    </x:row>
+    <x:row r="2" ht="42" customHeight="1">
+      <x:c r="A2" s="98" t="str">
+        <x:v>Les trois tableaux ci-dessous sont trois lectures des mêmes 6 500 unités : par référence, par lot et par atelier. Ne les additionnez pas entre eux. Les colonnes « Nombre de retours » et « Taux de retours » sont à compléter à partir de l’onglet « Retours_clients ».</x:v>
+      </x:c>
+      <x:c r="B2" s="98" t="str">
+        <x:v>Les trois tableaux ci-dessous sont trois lectures des mêmes 6 500 unités : par référence, par lot et par atelier. Ne les additionnez pas entre eux. Les colonnes « Nombre de retours » et « Taux de retours » sont à compléter à partir de l’onglet « Retours_clients ».</x:v>
+      </x:c>
+      <x:c r="C2" s="98" t="str">
+        <x:v>Les trois tableaux ci-dessous sont trois lectures des mêmes 6 500 unités : par référence, par lot et par atelier. Ne les additionnez pas entre eux. Les colonnes « Nombre de retours » et « Taux de retours » sont à compléter à partir de l’onglet « Retours_clients ».</x:v>
+      </x:c>
+      <x:c r="D2" s="98" t="str">
+        <x:v>Les trois tableaux ci-dessous sont trois lectures des mêmes 6 500 unités : par référence, par lot et par atelier. Ne les additionnez pas entre eux. Les colonnes « Nombre de retours » et « Taux de retours » sont à compléter à partir de l’onglet « Retours_clients ».</x:v>
+      </x:c>
+      <x:c r="E2" s="98" t="str">
+        <x:v>Les trois tableaux ci-dessous sont trois lectures des mêmes 6 500 unités : par référence, par lot et par atelier. Ne les additionnez pas entre eux. Les colonnes « Nombre de retours » et « Taux de retours » sont à compléter à partir de l’onglet « Retours_clients ».</x:v>
+      </x:c>
+      <x:c r="F2" s="98" t="str">
+        <x:v>Les trois tableaux ci-dessous sont trois lectures des mêmes 6 500 unités : par référence, par lot et par atelier. Ne les additionnez pas entre eux. Les colonnes « Nombre de retours » et « Taux de retours » sont à compléter à partir de l’onglet « Retours_clients ».</x:v>
+      </x:c>
+      <x:c r="G2" s="98" t="str">
+        <x:v>Les trois tableaux ci-dessous sont trois lectures des mêmes 6 500 unités : par référence, par lot et par atelier. Ne les additionnez pas entre eux. Les colonnes « Nombre de retours » et « Taux de retours » sont à compléter à partir de l’onglet « Retours_clients ».</x:v>
+      </x:c>
+      <x:c r="H2" s="98" t="str">
+        <x:v>Les trois tableaux ci-dessous sont trois lectures des mêmes 6 500 unités : par référence, par lot et par atelier. Ne les additionnez pas entre eux. Les colonnes « Nombre de retours » et « Taux de retours » sont à compléter à partir de l’onglet « Retours_clients ».</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="92" t="str">
+        <x:v>Référence pédagogique</x:v>
+      </x:c>
+      <x:c r="B4" s="92" t="str">
+        <x:v>Unités vendues</x:v>
+      </x:c>
+      <x:c r="C4" s="92" t="str">
+        <x:v>Nombre de retours</x:v>
+      </x:c>
+      <x:c r="D4" s="92" t="str">
+        <x:v>Taux de retours</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" t="str">
+        <x:v>J-101</x:v>
+      </x:c>
+      <x:c r="B5" t="n">
+        <x:v>900</x:v>
+      </x:c>
+      <x:c r="C5"/>
+      <x:c r="D5" s="99"/>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" t="str">
+        <x:v>J-102</x:v>
+      </x:c>
+      <x:c r="B6" t="n">
+        <x:v>1350</x:v>
+      </x:c>
+      <x:c r="C6"/>
+      <x:c r="D6" s="99"/>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" t="str">
+        <x:v>J-201</x:v>
+      </x:c>
+      <x:c r="B7" t="n">
+        <x:v>1450</x:v>
+      </x:c>
+      <x:c r="C7"/>
+      <x:c r="D7" s="99"/>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" t="str">
+        <x:v>V-401</x:v>
+      </x:c>
+      <x:c r="B8" t="n">
+        <x:v>1700</x:v>
+      </x:c>
+      <x:c r="C8"/>
+      <x:c r="D8" s="99"/>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" t="str">
+        <x:v>CH-301</x:v>
+      </x:c>
+      <x:c r="B9" t="n">
+        <x:v>1100</x:v>
+      </x:c>
+      <x:c r="C9"/>
+      <x:c r="D9" s="99"/>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="92" t="str">
+        <x:v>Lot</x:v>
+      </x:c>
+      <x:c r="B12" s="92" t="str">
+        <x:v>Unités du lot</x:v>
+      </x:c>
+      <x:c r="C12" s="92" t="str">
+        <x:v>Nombre de retours</x:v>
+      </x:c>
+      <x:c r="D12" s="92" t="str">
+        <x:v>Taux de retours</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" t="str">
+        <x:v>L26-06</x:v>
+      </x:c>
+      <x:c r="B13" t="n">
+        <x:v>1500</x:v>
+      </x:c>
+      <x:c r="C13"/>
+      <x:c r="D13" s="99"/>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" t="str">
+        <x:v>L26-07</x:v>
+      </x:c>
+      <x:c r="B14" t="n">
+        <x:v>1650</x:v>
+      </x:c>
+      <x:c r="C14"/>
+      <x:c r="D14" s="99"/>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" t="str">
+        <x:v>L26-08</x:v>
+      </x:c>
+      <x:c r="B15" t="n">
+        <x:v>1750</x:v>
+      </x:c>
+      <x:c r="C15"/>
+      <x:c r="D15" s="99"/>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" t="str">
+        <x:v>L26-09</x:v>
+      </x:c>
+      <x:c r="B16" t="n">
+        <x:v>1600</x:v>
+      </x:c>
+      <x:c r="C16"/>
+      <x:c r="D16" s="99"/>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="92" t="str">
+        <x:v>Atelier pédagogique</x:v>
+      </x:c>
+      <x:c r="B20" s="92" t="str">
+        <x:v>Unités produites</x:v>
+      </x:c>
+      <x:c r="C20" s="92" t="str">
+        <x:v>Nombre de retours</x:v>
+      </x:c>
+      <x:c r="D20" s="92" t="str">
+        <x:v>Taux de retours</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" t="str">
+        <x:v>Atelier A</x:v>
+      </x:c>
+      <x:c r="B21" t="n">
+        <x:v>1650</x:v>
+      </x:c>
+      <x:c r="C21"/>
+      <x:c r="D21" s="99"/>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" t="str">
+        <x:v>Atelier B</x:v>
+      </x:c>
+      <x:c r="B22" t="n">
+        <x:v>1700</x:v>
+      </x:c>
+      <x:c r="C22"/>
+      <x:c r="D22" s="99"/>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" t="str">
+        <x:v>Atelier C</x:v>
+      </x:c>
+      <x:c r="B23" t="n">
+        <x:v>1600</x:v>
+      </x:c>
+      <x:c r="C23"/>
+      <x:c r="D23" s="99"/>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" t="str">
+        <x:v>Atelier D</x:v>
+      </x:c>
+      <x:c r="B24" t="n">
+        <x:v>1550</x:v>
+      </x:c>
+      <x:c r="C24"/>
+      <x:c r="D24" s="99"/>
+    </x:row>
+    <x:row r="28" ht="42" customHeight="1">
+      <x:c r="A28" s="98" t="str">
+        <x:v>DONNÉE COMPLÉMENTAIRE À UTILISER APRÈS VOTRE PREMIER TRI : 520 unités J-101 du lot L26-08 ont été produites par l’Atelier C. À vous de retrouver dans « Retours_clients » le nombre de retours correspondant et la part liée au motif « Couture ».</x:v>
+      </x:c>
+      <x:c r="B28" s="98" t="str">
+        <x:v>DONNÉE COMPLÉMENTAIRE À UTILISER APRÈS VOTRE PREMIER TRI : 520 unités J-101 du lot L26-08 ont été produites par l’Atelier C. À vous de retrouver dans « Retours_clients » le nombre de retours correspondant et la part liée au motif « Couture ».</x:v>
+      </x:c>
+      <x:c r="C28" s="98" t="str">
+        <x:v>DONNÉE COMPLÉMENTAIRE À UTILISER APRÈS VOTRE PREMIER TRI : 520 unités J-101 du lot L26-08 ont été produites par l’Atelier C. À vous de retrouver dans « Retours_clients » le nombre de retours correspondant et la part liée au motif « Couture ».</x:v>
+      </x:c>
+      <x:c r="D28" s="98" t="str">
+        <x:v>DONNÉE COMPLÉMENTAIRE À UTILISER APRÈS VOTRE PREMIER TRI : 520 unités J-101 du lot L26-08 ont été produites par l’Atelier C. À vous de retrouver dans « Retours_clients » le nombre de retours correspondant et la part liée au motif « Couture ».</x:v>
+      </x:c>
+      <x:c r="E28" s="98" t="str">
+        <x:v>DONNÉE COMPLÉMENTAIRE À UTILISER APRÈS VOTRE PREMIER TRI : 520 unités J-101 du lot L26-08 ont été produites par l’Atelier C. À vous de retrouver dans « Retours_clients » le nombre de retours correspondant et la part liée au motif « Couture ».</x:v>
+      </x:c>
+      <x:c r="F28" s="98" t="str">
+        <x:v>DONNÉE COMPLÉMENTAIRE À UTILISER APRÈS VOTRE PREMIER TRI : 520 unités J-101 du lot L26-08 ont été produites par l’Atelier C. À vous de retrouver dans « Retours_clients » le nombre de retours correspondant et la part liée au motif « Couture ».</x:v>
+      </x:c>
+      <x:c r="G28" s="98" t="str">
+        <x:v>DONNÉE COMPLÉMENTAIRE À UTILISER APRÈS VOTRE PREMIER TRI : 520 unités J-101 du lot L26-08 ont été produites par l’Atelier C. À vous de retrouver dans « Retours_clients » le nombre de retours correspondant et la part liée au motif « Couture ».</x:v>
+      </x:c>
+      <x:c r="H28" s="98" t="str">
+        <x:v>DONNÉE COMPLÉMENTAIRE À UTILISER APRÈS VOTRE PREMIER TRI : 520 unités J-101 du lot L26-08 ont été produites par l’Atelier C. À vous de retrouver dans « Retours_clients » le nombre de retours correspondant et la part liée au motif « Couture ».</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="92" t="str">
+        <x:v>Périmètre ciblé</x:v>
+      </x:c>
+      <x:c r="B30" s="92" t="str">
+        <x:v>Unités exposées</x:v>
+      </x:c>
+      <x:c r="C30" s="92" t="str">
+        <x:v>Retours totaux</x:v>
+      </x:c>
+      <x:c r="D30" s="92" t="str">
+        <x:v>Retours motif « Couture »</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" t="str">
+        <x:v>J-101 · L26-08 · Atelier C</x:v>
+      </x:c>
+      <x:c r="B31" t="n">
+        <x:v>520</x:v>
+      </x:c>
+      <x:c r="C31"/>
+      <x:c r="D31"/>
+    </x:row>
+    <x:row r="33" ht="42" customHeight="1">
+      <x:c r="A33" s="98" t="str">
+        <x:v>Attention : cette concentration oriente l’enquête ; elle ne démontre pas à elle seule la cause du dysfonctionnement.</x:v>
+      </x:c>
+      <x:c r="B33" s="98"/>
+      <x:c r="C33" s="98"/>
+      <x:c r="D33" s="98"/>
+      <x:c r="E33" s="98"/>
+      <x:c r="F33" s="98"/>
+      <x:c r="G33" s="98"/>
+      <x:c r="H33" s="98"/>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:H1"/>
+    <x:mergeCell ref="A2:H2"/>
+    <x:mergeCell ref="A28:H28"/>
+    <x:mergeCell ref="A33:H33"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="34" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="48" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="16" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="26" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="46" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="46" customHeight="1">
+      <x:c r="A1" s="95" t="str">
+        <x:v>SITUATION 6 — ÉLÉMENTS DE DIAGNOSTIC COMPLÉMENTAIRE. Toutes les pièces et mesures ci-dessous sont fictives.</x:v>
+      </x:c>
+      <x:c r="B1" s="95"/>
+      <x:c r="C1" s="95"/>
+      <x:c r="D1" s="95"/>
+      <x:c r="E1" s="95"/>
+      <x:c r="F1" s="95"/>
+    </x:row>
+    <x:row r="2" ht="46" customHeight="1">
+      <x:c r="A2" s="98" t="str">
+        <x:v>Ces éléments sont fournis pour tester les hypothèses issues de l’analyse des retours. Distinguez ce qu’ils permettent d’établir, ce qu’ils rendent probable et ce qu’ils ne permettent toujours pas d’affirmer.</x:v>
+      </x:c>
+      <x:c r="B2" s="98"/>
+      <x:c r="C2" s="98"/>
+      <x:c r="D2" s="98"/>
+      <x:c r="E2" s="98"/>
+      <x:c r="F2" s="98"/>
+    </x:row>
+    <x:row r="4" ht="42" customHeight="1">
+      <x:c r="A4" s="92" t="str">
+        <x:v>Élément contrôlé</x:v>
+      </x:c>
+      <x:c r="B4" s="92" t="str">
+        <x:v>Périmètre</x:v>
+      </x:c>
+      <x:c r="C4" s="92" t="str">
+        <x:v>Résultat factuel</x:v>
+      </x:c>
+      <x:c r="D4" s="92" t="str">
+        <x:v>Date</x:v>
+      </x:c>
+      <x:c r="E4" s="92" t="str">
+        <x:v>Type de preuve</x:v>
+      </x:c>
+      <x:c r="F4" s="92" t="str">
+        <x:v>Limite / prudence</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="82" customHeight="1">
+      <x:c r="A5" s="50" t="str">
+        <x:v>Procédure QUA-COUT-04</x:v>
+      </x:c>
+      <x:c r="B5" s="50" t="str">
+        <x:v>Contrôle couture</x:v>
+      </x:c>
+      <x:c r="C5" s="50" t="str">
+        <x:v>La tension de fil attendue est comprise entre 2,4 et 2,6. Un contrôle doit être tracé au démarrage de chaque lot et après changement de fil ou de matière.</x:v>
+      </x:c>
+      <x:c r="D5" s="50" t="str">
+        <x:v>05/09/2026</x:v>
+      </x:c>
+      <x:c r="E5" s="50" t="str">
+        <x:v>Procédure interne simulée</x:v>
+      </x:c>
+      <x:c r="F5" s="50" t="str">
+        <x:v>La procédure décrit ce qui est attendu ; elle ne prouve pas que le contrôle a été réalisé.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="82" customHeight="1">
+      <x:c r="A6" s="50" t="str">
+        <x:v>Fiche de démarrage</x:v>
+      </x:c>
+      <x:c r="B6" s="50" t="str">
+        <x:v>J-101 · L26-08 · Atelier C · poste C-04</x:v>
+      </x:c>
+      <x:c r="C6" s="50" t="str">
+        <x:v>Aucune trace de contrôle de tension n’a été retrouvée au démarrage du lot.</x:v>
+      </x:c>
+      <x:c r="D6" s="50" t="str">
+        <x:v>05/09/2026</x:v>
+      </x:c>
+      <x:c r="E6" s="50" t="str">
+        <x:v>Enregistrement interne simulé</x:v>
+      </x:c>
+      <x:c r="F6" s="50" t="str">
+        <x:v>Absence de trace ≠ preuve certaine d’absence d’action ; il faut recouper.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="82" customHeight="1">
+      <x:c r="A7" s="50" t="str">
+        <x:v>Contrôle maintenance</x:v>
+      </x:c>
+      <x:c r="B7" s="50" t="str">
+        <x:v>Poste C-04</x:v>
+      </x:c>
+      <x:c r="C7" s="50" t="str">
+        <x:v>Tension mesurée à 3,2. Aucun organe mécanique cassé n’est identifié.</x:v>
+      </x:c>
+      <x:c r="D7" s="50" t="str">
+        <x:v>06/09/2026</x:v>
+      </x:c>
+      <x:c r="E7" s="50" t="str">
+        <x:v>Compte rendu maintenance simulé</x:v>
+      </x:c>
+      <x:c r="F7" s="50" t="str">
+        <x:v>Mesure réalisée après apparition du problème ; elle doit être rapprochée d’autres éléments.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="82" customHeight="1">
+      <x:c r="A8" s="50" t="str">
+        <x:v>Échantillon avant réglage</x:v>
+      </x:c>
+      <x:c r="B8" s="50" t="str">
+        <x:v>J-101 · L26-08 · Atelier C · poste C-04</x:v>
+      </x:c>
+      <x:c r="C8" s="50" t="str">
+        <x:v>40 pièces contrôlées : 6 non-conformités de couture ciblées.</x:v>
+      </x:c>
+      <x:c r="D8" s="50" t="str">
+        <x:v>06/09/2026</x:v>
+      </x:c>
+      <x:c r="E8" s="50" t="str">
+        <x:v>Contrôle qualité simulé</x:v>
+      </x:c>
+      <x:c r="F8" s="50" t="str">
+        <x:v>Échantillon limité à 40 pièces.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="82" customHeight="1">
+      <x:c r="A9" s="50" t="str">
+        <x:v>Échantillon comparatif</x:v>
+      </x:c>
+      <x:c r="B9" s="50" t="str">
+        <x:v>Même référence et lot · poste C-02</x:v>
+      </x:c>
+      <x:c r="C9" s="50" t="str">
+        <x:v>40 pièces contrôlées : 1 non-conformité de couture ciblée.</x:v>
+      </x:c>
+      <x:c r="D9" s="50" t="str">
+        <x:v>06/09/2026</x:v>
+      </x:c>
+      <x:c r="E9" s="50" t="str">
+        <x:v>Contrôle qualité simulé</x:v>
+      </x:c>
+      <x:c r="F9" s="50" t="str">
+        <x:v>Comparaison utile mais un autre poste peut différer sur plusieurs paramètres.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="82" customHeight="1">
+      <x:c r="A10" s="50" t="str">
+        <x:v>Test après remise au réglage standard</x:v>
+      </x:c>
+      <x:c r="B10" s="50" t="str">
+        <x:v>J-101 · L26-08 · poste C-04</x:v>
+      </x:c>
+      <x:c r="C10" s="50" t="str">
+        <x:v>40 pièces contrôlées : 1 non-conformité de couture ciblée.</x:v>
+      </x:c>
+      <x:c r="D10" s="50" t="str">
+        <x:v>07/09/2026</x:v>
+      </x:c>
+      <x:c r="E10" s="50" t="str">
+        <x:v>Test qualité simulé</x:v>
+      </x:c>
+      <x:c r="F10" s="50" t="str">
+        <x:v>Résultat encourageant à confirmer sur une durée plus longue.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="48" customHeight="1">
+      <x:c r="A12" s="102" t="str">
+        <x:v>Travail attendu : reliez ces éléments aux données de retours, classez vos hypothèses (écartées / plausibles / étayées) et formulez une conclusion proportionnée aux preuves.</x:v>
+      </x:c>
+      <x:c r="B12" s="102"/>
+      <x:c r="C12" s="102"/>
+      <x:c r="D12" s="102"/>
+      <x:c r="E12" s="102"/>
+      <x:c r="F12" s="102"/>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:F1"/>
+    <x:mergeCell ref="A2:F2"/>
+    <x:mergeCell ref="A12:F12"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
 </file>